--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1583,6 +1583,4175 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129145512</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>581002</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6952394</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129145329</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>581027</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6952418</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129147978</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91485</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>581098</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6952295</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129145962</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57564</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>580975</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6952488</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129147195</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>658</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>581017</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6952357</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129147106</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>658</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>581035</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6952380</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129146939</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91975</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>580964</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6952430</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129147920</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>581077</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6952314</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129145861</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>580975</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6952488</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129147319</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>658</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>581032</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6952316</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129146554</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>580964</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6952430</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129146985</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>658</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>581008</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6952388</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129146915</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>658</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>580964</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6952430</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129145834</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>580977</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6952440</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129145307</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91721</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>48</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>581027</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6952418</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129147254</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80139</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>581037</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6952341</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129147966</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91975</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>581110</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6952279</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129147908</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98651</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>581062</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6952301</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129146557</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>658</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>580965</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6952443</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129146457</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98651</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>580954</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6952482</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129147381</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>581041</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6952272</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129147019</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>581016</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6952378</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129145352</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>581021</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6952419</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129147282</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>581043</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6952312</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129145294</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>658</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>581027</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6952418</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129147892</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>581048</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6952301</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129148349</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91721</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>48</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>581129</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6952292</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129145405</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>581012</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6952414</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129147052</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>898</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>581016</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6952378</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129146510</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98651</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>580968</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6952454</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129147948</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>658</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>581098</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6952295</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129147998</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>581110</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6952279</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129145366</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>658</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>581021</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6952419</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129145777</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>658</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>580994</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6952436</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129147111</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>581035</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6952380</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129147338</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>581035</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6952297</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129147161</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>581019</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6952367</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129145829</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98651</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>580986</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6952449</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129147223</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>581028</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6952359</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129147435</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>658</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>581012</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6952237</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129147878</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>581069</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6952305</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129148498</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92143</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>483</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rostskinn</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Crustoderma dryinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Drolsviken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>581137</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6952306</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,32 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145512</v>
+        <v>129147978</v>
       </c>
       <c r="B11" t="n">
-        <v>91520</v>
+        <v>91488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581002</v>
+        <v>581098</v>
       </c>
       <c r="R11" t="n">
-        <v>6952394</v>
+        <v>6952295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,45 +1682,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145329</v>
+        <v>129145962</v>
       </c>
       <c r="B12" t="n">
-        <v>91520</v>
+        <v>57564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581027</v>
+        <v>580975</v>
       </c>
       <c r="R12" t="n">
-        <v>6952418</v>
+        <v>6952488</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1788,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147978</v>
+        <v>129145329</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>91523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581098</v>
+        <v>581027</v>
       </c>
       <c r="R13" t="n">
-        <v>6952295</v>
+        <v>6952418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,54 +1885,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129145962</v>
+        <v>129147195</v>
       </c>
       <c r="B14" t="n">
-        <v>57564</v>
+        <v>91808</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580975</v>
+        <v>581017</v>
       </c>
       <c r="R14" t="n">
-        <v>6952488</v>
+        <v>6952357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147195</v>
+        <v>129145512</v>
       </c>
       <c r="B15" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581017</v>
+        <v>581002</v>
       </c>
       <c r="R15" t="n">
-        <v>6952357</v>
+        <v>6952394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,7 +2082,7 @@
         <v>129147106</v>
       </c>
       <c r="B16" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129146939</v>
+        <v>129147920</v>
       </c>
       <c r="B17" t="n">
-        <v>91975</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580964</v>
+        <v>581077</v>
       </c>
       <c r="R17" t="n">
-        <v>6952430</v>
+        <v>6952314</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129147920</v>
+        <v>129146939</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>91978</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581077</v>
+        <v>580964</v>
       </c>
       <c r="R18" t="n">
-        <v>6952314</v>
+        <v>6952430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129147319</v>
+        <v>129146985</v>
       </c>
       <c r="B20" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581032</v>
+        <v>581008</v>
       </c>
       <c r="R20" t="n">
-        <v>6952316</v>
+        <v>6952388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146554</v>
+        <v>129146915</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146985</v>
+        <v>129147319</v>
       </c>
       <c r="B22" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581008</v>
+        <v>581032</v>
       </c>
       <c r="R22" t="n">
-        <v>6952388</v>
+        <v>6952316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146915</v>
+        <v>129146554</v>
       </c>
       <c r="B23" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2865,50 +2865,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145834</v>
+        <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>91978</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580977</v>
+        <v>581110</v>
       </c>
       <c r="R24" t="n">
-        <v>6952440</v>
+        <v>6952279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,11 +2936,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2975,7 +2965,7 @@
         <v>129145307</v>
       </c>
       <c r="B25" t="n">
-        <v>91721</v>
+        <v>91724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,45 +3156,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129147966</v>
+        <v>129145834</v>
       </c>
       <c r="B27" t="n">
-        <v>91975</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581110</v>
+        <v>580977</v>
       </c>
       <c r="R27" t="n">
-        <v>6952279</v>
+        <v>6952440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,6 +3232,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,45 +3364,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B29" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R29" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,49 +3465,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R30" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,7 +3672,7 @@
         <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>91721</v>
+        <v>91724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129145366</v>
+        <v>129147161</v>
       </c>
       <c r="B43" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581021</v>
+        <v>581019</v>
       </c>
       <c r="R43" t="n">
-        <v>6952419</v>
+        <v>6952367</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145777</v>
+        <v>129147111</v>
       </c>
       <c r="B44" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580994</v>
+        <v>581035</v>
       </c>
       <c r="R44" t="n">
-        <v>6952436</v>
+        <v>6952380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147111</v>
+        <v>129145777</v>
       </c>
       <c r="B45" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581035</v>
+        <v>580994</v>
       </c>
       <c r="R45" t="n">
-        <v>6952380</v>
+        <v>6952436</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5064,7 +5064,7 @@
         <v>129147338</v>
       </c>
       <c r="B46" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129147161</v>
+        <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581019</v>
+        <v>581021</v>
       </c>
       <c r="R47" t="n">
-        <v>6952367</v>
+        <v>6952419</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129145829</v>
+        <v>129148498</v>
       </c>
       <c r="B48" t="n">
-        <v>98651</v>
+        <v>92148</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,38 +5266,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580986</v>
+        <v>581137</v>
       </c>
       <c r="R48" t="n">
-        <v>6952449</v>
+        <v>6952306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5356,10 +5352,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147223</v>
+        <v>129147878</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>91523</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,39 +5363,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581028</v>
+        <v>581069</v>
       </c>
       <c r="R49" t="n">
-        <v>6952359</v>
+        <v>6952305</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5432,11 +5423,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5466,7 +5452,7 @@
         <v>129147435</v>
       </c>
       <c r="B50" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5560,10 +5546,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147878</v>
+        <v>129147223</v>
       </c>
       <c r="B51" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5571,34 +5557,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581069</v>
+        <v>581028</v>
       </c>
       <c r="R51" t="n">
-        <v>6952305</v>
+        <v>6952359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5631,6 +5622,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5657,10 +5653,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129148498</v>
+        <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>92143</v>
+        <v>98656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5668,34 +5664,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581137</v>
+        <v>580986</v>
       </c>
       <c r="R52" t="n">
-        <v>6952306</v>
+        <v>6952449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>129013342</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>129013314</v>
       </c>
       <c r="B9" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,32 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147978</v>
+        <v>129145329</v>
       </c>
       <c r="B11" t="n">
-        <v>91488</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581098</v>
+        <v>581027</v>
       </c>
       <c r="R11" t="n">
-        <v>6952295</v>
+        <v>6952418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,54 +1682,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145962</v>
+        <v>129145512</v>
       </c>
       <c r="B12" t="n">
-        <v>57564</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580975</v>
+        <v>581002</v>
       </c>
       <c r="R12" t="n">
-        <v>6952488</v>
+        <v>6952394</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145329</v>
+        <v>129147195</v>
       </c>
       <c r="B13" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581027</v>
+        <v>581017</v>
       </c>
       <c r="R13" t="n">
-        <v>6952418</v>
+        <v>6952357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147195</v>
+        <v>129147106</v>
       </c>
       <c r="B14" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581017</v>
+        <v>581035</v>
       </c>
       <c r="R14" t="n">
-        <v>6952357</v>
+        <v>6952380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129145512</v>
+        <v>129147978</v>
       </c>
       <c r="B15" t="n">
-        <v>91523</v>
+        <v>91491</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581002</v>
+        <v>581098</v>
       </c>
       <c r="R15" t="n">
-        <v>6952394</v>
+        <v>6952295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,45 +2070,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129147106</v>
+        <v>129145962</v>
       </c>
       <c r="B16" t="n">
-        <v>91808</v>
+        <v>57564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>102621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581035</v>
+        <v>580975</v>
       </c>
       <c r="R16" t="n">
-        <v>6952380</v>
+        <v>6952488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129147920</v>
+        <v>129146939</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>91981</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581077</v>
+        <v>580964</v>
       </c>
       <c r="R17" t="n">
-        <v>6952314</v>
+        <v>6952430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129146939</v>
+        <v>129147920</v>
       </c>
       <c r="B18" t="n">
-        <v>91978</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580964</v>
+        <v>581077</v>
       </c>
       <c r="R18" t="n">
-        <v>6952430</v>
+        <v>6952314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129145861</v>
+        <v>129146985</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,39 +2381,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580975</v>
+        <v>581008</v>
       </c>
       <c r="R19" t="n">
-        <v>6952488</v>
+        <v>6952388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,11 +2441,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2477,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146985</v>
+        <v>129146915</v>
       </c>
       <c r="B20" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2512,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R20" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146915</v>
+        <v>129147319</v>
       </c>
       <c r="B21" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R21" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2671,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129147319</v>
+        <v>129146554</v>
       </c>
       <c r="B22" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2672,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2696,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R22" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146554</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,45 +2865,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147966</v>
+        <v>129145834</v>
       </c>
       <c r="B24" t="n">
-        <v>91978</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581110</v>
+        <v>580977</v>
       </c>
       <c r="R24" t="n">
-        <v>6952279</v>
+        <v>6952440</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,6 +2941,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2965,7 +2975,7 @@
         <v>129145307</v>
       </c>
       <c r="B25" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3059,32 +3069,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147254</v>
+        <v>129147966</v>
       </c>
       <c r="B26" t="n">
-        <v>80139</v>
+        <v>91981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3104,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581037</v>
+        <v>581110</v>
       </c>
       <c r="R26" t="n">
-        <v>6952341</v>
+        <v>6952279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3156,10 +3166,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145834</v>
+        <v>129147254</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,39 +3177,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580977</v>
+        <v>581037</v>
       </c>
       <c r="R27" t="n">
-        <v>6952440</v>
+        <v>6952341</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,11 +3237,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,49 +3364,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R29" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3465,45 +3461,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R30" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B32" t="n">
-        <v>91978</v>
+        <v>91526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R32" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B33" t="n">
-        <v>91523</v>
+        <v>91981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R33" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B37" t="n">
-        <v>91724</v>
+        <v>91981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R37" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B38" t="n">
-        <v>91978</v>
+        <v>91727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R38" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>129147161</v>
       </c>
       <c r="B43" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129147111</v>
       </c>
       <c r="B44" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>129145777</v>
       </c>
       <c r="B45" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>129147338</v>
       </c>
       <c r="B46" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5255,32 +5255,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129148498</v>
+        <v>129147878</v>
       </c>
       <c r="B48" t="n">
-        <v>92148</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581137</v>
+        <v>581069</v>
       </c>
       <c r="R48" t="n">
-        <v>6952306</v>
+        <v>6952305</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147878</v>
+        <v>129147223</v>
       </c>
       <c r="B49" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,34 +5363,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581069</v>
+        <v>581028</v>
       </c>
       <c r="R49" t="n">
-        <v>6952305</v>
+        <v>6952359</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5423,6 +5428,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5449,45 +5459,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147435</v>
+        <v>129145829</v>
       </c>
       <c r="B50" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581012</v>
+        <v>580986</v>
       </c>
       <c r="R50" t="n">
-        <v>6952237</v>
+        <v>6952449</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5546,50 +5560,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147223</v>
+        <v>129148498</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>92151</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>483</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581028</v>
+        <v>581137</v>
       </c>
       <c r="R51" t="n">
-        <v>6952359</v>
+        <v>6952306</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5622,11 +5631,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5653,49 +5657,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129145829</v>
+        <v>129147435</v>
       </c>
       <c r="B52" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580986</v>
+        <v>581012</v>
       </c>
       <c r="R52" t="n">
-        <v>6952449</v>
+        <v>6952237</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145329</v>
+        <v>129147195</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581027</v>
+        <v>581017</v>
       </c>
       <c r="R11" t="n">
-        <v>6952418</v>
+        <v>6952357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147195</v>
+        <v>129147106</v>
       </c>
       <c r="B13" t="n">
         <v>91811</v>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581017</v>
+        <v>581035</v>
       </c>
       <c r="R13" t="n">
-        <v>6952357</v>
+        <v>6952380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,32 +1876,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147106</v>
+        <v>129147978</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>91491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581035</v>
+        <v>581098</v>
       </c>
       <c r="R14" t="n">
-        <v>6952380</v>
+        <v>6952295</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147978</v>
+        <v>129145329</v>
       </c>
       <c r="B15" t="n">
-        <v>91491</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581098</v>
+        <v>581027</v>
       </c>
       <c r="R15" t="n">
-        <v>6952295</v>
+        <v>6952418</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146985</v>
+        <v>129145861</v>
       </c>
       <c r="B19" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,34 +2381,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581008</v>
+        <v>580975</v>
       </c>
       <c r="R19" t="n">
-        <v>6952388</v>
+        <v>6952488</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,6 +2446,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2467,7 +2477,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146915</v>
+        <v>129146985</v>
       </c>
       <c r="B20" t="n">
         <v>91811</v>
@@ -2502,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R20" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,7 +2574,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B21" t="n">
         <v>91811</v>
@@ -2599,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R21" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146554</v>
+        <v>129147319</v>
       </c>
       <c r="B22" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2696,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R22" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2758,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129145861</v>
+        <v>129146554</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,39 +2779,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R23" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,50 +2865,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145834</v>
+        <v>129145307</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>91727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580977</v>
+        <v>581027</v>
       </c>
       <c r="R24" t="n">
-        <v>6952440</v>
+        <v>6952418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,11 +2936,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2972,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B25" t="n">
-        <v>91727</v>
+        <v>91981</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2983,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3007,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R25" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,32 +3059,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147966</v>
+        <v>129147254</v>
       </c>
       <c r="B26" t="n">
-        <v>91981</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3104,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581110</v>
+        <v>581037</v>
       </c>
       <c r="R26" t="n">
-        <v>6952279</v>
+        <v>6952341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3166,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129147254</v>
+        <v>129145834</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3177,34 +3167,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581037</v>
+        <v>580977</v>
       </c>
       <c r="R27" t="n">
-        <v>6952341</v>
+        <v>6952440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,6 +3232,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3364,45 +3364,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B29" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R29" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,49 +3465,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R30" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91526</v>
+        <v>91981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R32" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91981</v>
+        <v>91526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R33" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>91981</v>
+        <v>91727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R37" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>91727</v>
+        <v>91981</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R38" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129147161</v>
+        <v>129145777</v>
       </c>
       <c r="B43" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581019</v>
+        <v>580994</v>
       </c>
       <c r="R43" t="n">
-        <v>6952367</v>
+        <v>6952436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129147111</v>
+        <v>129145366</v>
       </c>
       <c r="B44" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R44" t="n">
-        <v>6952380</v>
+        <v>6952419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129145777</v>
+        <v>129147161</v>
       </c>
       <c r="B45" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580994</v>
+        <v>581019</v>
       </c>
       <c r="R45" t="n">
-        <v>6952436</v>
+        <v>6952367</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147338</v>
+        <v>129147111</v>
       </c>
       <c r="B46" t="n">
         <v>91526</v>
@@ -5099,7 +5099,7 @@
         <v>581035</v>
       </c>
       <c r="R46" t="n">
-        <v>6952297</v>
+        <v>6952380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129145366</v>
+        <v>129147338</v>
       </c>
       <c r="B47" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R47" t="n">
-        <v>6952419</v>
+        <v>6952297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5255,32 +5255,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129147878</v>
+        <v>129148498</v>
       </c>
       <c r="B48" t="n">
-        <v>91526</v>
+        <v>92151</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581069</v>
+        <v>581137</v>
       </c>
       <c r="R48" t="n">
-        <v>6952305</v>
+        <v>6952306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147223</v>
+        <v>129147435</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,39 +5363,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581028</v>
+        <v>581012</v>
       </c>
       <c r="R49" t="n">
-        <v>6952359</v>
+        <v>6952237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5428,11 +5423,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5459,49 +5449,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129145829</v>
+        <v>129147878</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580986</v>
+        <v>581069</v>
       </c>
       <c r="R50" t="n">
-        <v>6952449</v>
+        <v>6952305</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5560,45 +5546,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129148498</v>
+        <v>129147223</v>
       </c>
       <c r="B51" t="n">
-        <v>92151</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>483</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581137</v>
+        <v>581028</v>
       </c>
       <c r="R51" t="n">
-        <v>6952306</v>
+        <v>6952359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5631,6 +5622,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5657,45 +5653,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129147435</v>
+        <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581012</v>
+        <v>580986</v>
       </c>
       <c r="R52" t="n">
-        <v>6952237</v>
+        <v>6952449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1285,45 +1285,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013342</v>
+        <v>129013448</v>
       </c>
       <c r="B8" t="n">
-        <v>80169</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R8" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,40 +1386,35 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013314</v>
+        <v>129013342</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1484,37 +1483,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013448</v>
+        <v>129013314</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R10" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147878</v>
+        <v>129147223</v>
       </c>
       <c r="B50" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5460,34 +5460,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581069</v>
+        <v>581028</v>
       </c>
       <c r="R50" t="n">
-        <v>6952305</v>
+        <v>6952359</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5520,6 +5525,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5546,38 +5556,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147223</v>
+        <v>129145829</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5586,10 +5595,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581028</v>
+        <v>580986</v>
       </c>
       <c r="R51" t="n">
-        <v>6952359</v>
+        <v>6952449</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5622,11 +5631,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5653,49 +5657,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129145829</v>
+        <v>129147878</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580986</v>
+        <v>581069</v>
       </c>
       <c r="R52" t="n">
-        <v>6952449</v>
+        <v>6952305</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1285,49 +1285,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013448</v>
+        <v>129013342</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>80169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R8" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,35 +1382,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013342</v>
+        <v>129013314</v>
       </c>
       <c r="B9" t="n">
-        <v>80169</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1483,38 +1484,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013314</v>
+        <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R10" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,45 +1585,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147195</v>
+        <v>129145962</v>
       </c>
       <c r="B11" t="n">
-        <v>91811</v>
+        <v>57564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581017</v>
+        <v>580975</v>
       </c>
       <c r="R11" t="n">
-        <v>6952357</v>
+        <v>6952488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1691,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145512</v>
+        <v>129145329</v>
       </c>
       <c r="B12" t="n">
         <v>91526</v>
@@ -1717,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581002</v>
+        <v>581027</v>
       </c>
       <c r="R12" t="n">
-        <v>6952394</v>
+        <v>6952418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147106</v>
+        <v>129145512</v>
       </c>
       <c r="B13" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581035</v>
+        <v>581002</v>
       </c>
       <c r="R13" t="n">
-        <v>6952380</v>
+        <v>6952394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,32 +1885,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147978</v>
+        <v>129147195</v>
       </c>
       <c r="B14" t="n">
-        <v>91491</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581098</v>
+        <v>581017</v>
       </c>
       <c r="R14" t="n">
-        <v>6952295</v>
+        <v>6952357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129145329</v>
+        <v>129147106</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581027</v>
+        <v>581035</v>
       </c>
       <c r="R15" t="n">
-        <v>6952418</v>
+        <v>6952380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129145962</v>
+        <v>129147978</v>
       </c>
       <c r="B16" t="n">
-        <v>57564</v>
+        <v>91491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,43 +2090,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102621</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580975</v>
+        <v>581098</v>
       </c>
       <c r="R16" t="n">
-        <v>6952488</v>
+        <v>6952295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129145861</v>
+        <v>129147319</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,39 +2381,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580975</v>
+        <v>581032</v>
       </c>
       <c r="R19" t="n">
-        <v>6952488</v>
+        <v>6952316</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,11 +2441,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2477,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146985</v>
+        <v>129146554</v>
       </c>
       <c r="B20" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R20" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146915</v>
+        <v>129145861</v>
       </c>
       <c r="B21" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,34 +2575,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R21" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,6 +2640,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2671,7 +2671,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129147319</v>
+        <v>129146985</v>
       </c>
       <c r="B22" t="n">
         <v>91811</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581032</v>
+        <v>581008</v>
       </c>
       <c r="R22" t="n">
-        <v>6952316</v>
+        <v>6952388</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146554</v>
+        <v>129146915</v>
       </c>
       <c r="B23" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147966</v>
+        <v>129147254</v>
       </c>
       <c r="B25" t="n">
-        <v>91981</v>
+        <v>80140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581110</v>
+        <v>581037</v>
       </c>
       <c r="R25" t="n">
-        <v>6952279</v>
+        <v>6952341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147254</v>
+        <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,34 +3070,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581037</v>
+        <v>580977</v>
       </c>
       <c r="R26" t="n">
-        <v>6952341</v>
+        <v>6952440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,6 +3135,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3156,50 +3166,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145834</v>
+        <v>129147966</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580977</v>
+        <v>581110</v>
       </c>
       <c r="R27" t="n">
-        <v>6952440</v>
+        <v>6952279</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,11 +3237,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3364,49 +3364,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R29" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3465,45 +3461,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R30" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B32" t="n">
-        <v>91981</v>
+        <v>91526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R32" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B33" t="n">
-        <v>91526</v>
+        <v>91981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R33" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B37" t="n">
-        <v>91727</v>
+        <v>91981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R37" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B38" t="n">
-        <v>91981</v>
+        <v>91727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R38" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147435</v>
+        <v>129147223</v>
       </c>
       <c r="B49" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,34 +5363,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581012</v>
+        <v>581028</v>
       </c>
       <c r="R49" t="n">
-        <v>6952237</v>
+        <v>6952359</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5423,6 +5428,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5449,10 +5459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147223</v>
+        <v>129147435</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5460,39 +5470,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581028</v>
+        <v>581012</v>
       </c>
       <c r="R50" t="n">
-        <v>6952359</v>
+        <v>6952237</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5525,11 +5530,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5556,49 +5556,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129145829</v>
+        <v>129147878</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580986</v>
+        <v>581069</v>
       </c>
       <c r="R51" t="n">
-        <v>6952449</v>
+        <v>6952305</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5657,45 +5653,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129147878</v>
+        <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581069</v>
+        <v>580986</v>
       </c>
       <c r="R52" t="n">
-        <v>6952305</v>
+        <v>6952449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>129013513</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129013351</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,45 +1285,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013342</v>
+        <v>129013448</v>
       </c>
       <c r="B8" t="n">
-        <v>80169</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R8" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,40 +1386,35 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013314</v>
+        <v>129013342</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1484,37 +1483,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013448</v>
+        <v>129013314</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R10" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,54 +1585,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145962</v>
+        <v>129147195</v>
       </c>
       <c r="B11" t="n">
-        <v>57564</v>
+        <v>91818</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580975</v>
+        <v>581017</v>
       </c>
       <c r="R11" t="n">
-        <v>6952488</v>
+        <v>6952357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145329</v>
+        <v>129147106</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581027</v>
+        <v>581035</v>
       </c>
       <c r="R12" t="n">
-        <v>6952418</v>
+        <v>6952380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145512</v>
+        <v>129145329</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581002</v>
+        <v>581027</v>
       </c>
       <c r="R13" t="n">
-        <v>6952394</v>
+        <v>6952418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147195</v>
+        <v>129145512</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581017</v>
+        <v>581002</v>
       </c>
       <c r="R14" t="n">
-        <v>6952357</v>
+        <v>6952394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147106</v>
+        <v>129147978</v>
       </c>
       <c r="B15" t="n">
-        <v>91811</v>
+        <v>91497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581035</v>
+        <v>581098</v>
       </c>
       <c r="R15" t="n">
-        <v>6952380</v>
+        <v>6952295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129147978</v>
+        <v>129145962</v>
       </c>
       <c r="B16" t="n">
-        <v>91491</v>
+        <v>57566</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,34 +2081,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>102621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581098</v>
+        <v>580975</v>
       </c>
       <c r="R16" t="n">
-        <v>6952295</v>
+        <v>6952488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
         <v>129146939</v>
       </c>
       <c r="B17" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>129147920</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129147319</v>
+        <v>129145861</v>
       </c>
       <c r="B19" t="n">
-        <v>91811</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,34 +2381,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581032</v>
+        <v>580975</v>
       </c>
       <c r="R19" t="n">
-        <v>6952316</v>
+        <v>6952488</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,6 +2446,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2467,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146554</v>
+        <v>129146985</v>
       </c>
       <c r="B20" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2488,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R20" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129145861</v>
+        <v>129146915</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>91818</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,39 +2585,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R21" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2640,11 +2645,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146985</v>
+        <v>129147319</v>
       </c>
       <c r="B22" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581008</v>
+        <v>581032</v>
       </c>
       <c r="R22" t="n">
-        <v>6952388</v>
+        <v>6952316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146915</v>
+        <v>129146554</v>
       </c>
       <c r="B23" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,7 +2868,7 @@
         <v>129145307</v>
       </c>
       <c r="B24" t="n">
-        <v>91727</v>
+        <v>91734</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147254</v>
+        <v>129147966</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>91988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581037</v>
+        <v>581110</v>
       </c>
       <c r="R25" t="n">
-        <v>6952341</v>
+        <v>6952279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129145834</v>
+        <v>129147254</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,39 +3070,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580977</v>
+        <v>581037</v>
       </c>
       <c r="R26" t="n">
-        <v>6952440</v>
+        <v>6952341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,11 +3130,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3166,45 +3156,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129147966</v>
+        <v>129145834</v>
       </c>
       <c r="B27" t="n">
-        <v>91981</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581110</v>
+        <v>580977</v>
       </c>
       <c r="R27" t="n">
-        <v>6952279</v>
+        <v>6952440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,6 +3232,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129147381</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91526</v>
+        <v>91988</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R32" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91981</v>
+        <v>91533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R33" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3866,7 +3866,7 @@
         <v>129147282</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129147892</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129145405</v>
       </c>
       <c r="B37" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129148349</v>
       </c>
       <c r="B38" t="n">
-        <v>91727</v>
+        <v>91734</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92199</v>
+        <v>92206</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>129147998</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>129145777</v>
       </c>
       <c r="B43" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129145366</v>
       </c>
       <c r="B44" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>129147161</v>
       </c>
       <c r="B45" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>129147111</v>
       </c>
       <c r="B46" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>129147338</v>
       </c>
       <c r="B47" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129148498</v>
+        <v>129145829</v>
       </c>
       <c r="B48" t="n">
-        <v>92151</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,34 +5266,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581137</v>
+        <v>580986</v>
       </c>
       <c r="R48" t="n">
-        <v>6952306</v>
+        <v>6952449</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5352,50 +5356,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147223</v>
+        <v>129148498</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>92158</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>483</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581028</v>
+        <v>581137</v>
       </c>
       <c r="R49" t="n">
-        <v>6952359</v>
+        <v>6952306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5428,11 +5427,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5462,7 +5456,7 @@
         <v>129147435</v>
       </c>
       <c r="B50" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5559,7 +5553,7 @@
         <v>129147878</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5653,37 +5647,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129145829</v>
+        <v>129147223</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580986</v>
+        <v>581028</v>
       </c>
       <c r="R52" t="n">
-        <v>6952449</v>
+        <v>6952359</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5728,6 +5723,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1285,49 +1285,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013448</v>
+        <v>129013342</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>80173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R8" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,35 +1382,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013342</v>
+        <v>129013314</v>
       </c>
       <c r="B9" t="n">
-        <v>80173</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1483,38 +1484,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013314</v>
+        <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R10" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129145861</v>
+        <v>129146554</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>91533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,39 +2381,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R19" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,11 +2441,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146554</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>91988</v>
+        <v>91734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R37" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>91734</v>
+        <v>91988</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R38" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129145829</v>
+        <v>129148498</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>92158</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,38 +5266,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580986</v>
+        <v>581137</v>
       </c>
       <c r="R48" t="n">
-        <v>6952449</v>
+        <v>6952306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5356,32 +5352,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129148498</v>
+        <v>129147435</v>
       </c>
       <c r="B49" t="n">
-        <v>92158</v>
+        <v>91818</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5391,10 +5387,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581137</v>
+        <v>581012</v>
       </c>
       <c r="R49" t="n">
-        <v>6952306</v>
+        <v>6952237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5453,10 +5449,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147435</v>
+        <v>129147878</v>
       </c>
       <c r="B50" t="n">
-        <v>91818</v>
+        <v>91533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5464,21 +5460,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5484,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581012</v>
+        <v>581069</v>
       </c>
       <c r="R50" t="n">
-        <v>6952237</v>
+        <v>6952305</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,10 +5546,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147878</v>
+        <v>129147223</v>
       </c>
       <c r="B51" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,34 +5557,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581069</v>
+        <v>581028</v>
       </c>
       <c r="R51" t="n">
-        <v>6952305</v>
+        <v>6952359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5621,6 +5622,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5647,38 +5653,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129147223</v>
+        <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5687,10 +5692,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581028</v>
+        <v>580986</v>
       </c>
       <c r="R52" t="n">
-        <v>6952359</v>
+        <v>6952449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5723,11 +5728,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,35 +1285,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013342</v>
+        <v>129013314</v>
       </c>
       <c r="B8" t="n">
-        <v>80173</v>
+        <v>80144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1382,40 +1387,35 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013314</v>
+        <v>129013342</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>80173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1487,7 +1487,7 @@
         <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,32 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147195</v>
+        <v>129147978</v>
       </c>
       <c r="B11" t="n">
-        <v>91818</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581017</v>
+        <v>581098</v>
       </c>
       <c r="R11" t="n">
-        <v>6952357</v>
+        <v>6952295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147106</v>
+        <v>129145329</v>
       </c>
       <c r="B12" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581035</v>
+        <v>581027</v>
       </c>
       <c r="R12" t="n">
-        <v>6952380</v>
+        <v>6952418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145329</v>
+        <v>129145512</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581027</v>
+        <v>581002</v>
       </c>
       <c r="R13" t="n">
-        <v>6952418</v>
+        <v>6952394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129145512</v>
+        <v>129147195</v>
       </c>
       <c r="B14" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581002</v>
+        <v>581017</v>
       </c>
       <c r="R14" t="n">
-        <v>6952394</v>
+        <v>6952357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147978</v>
+        <v>129147106</v>
       </c>
       <c r="B15" t="n">
-        <v>91497</v>
+        <v>91825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581098</v>
+        <v>581035</v>
       </c>
       <c r="R15" t="n">
-        <v>6952295</v>
+        <v>6952380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129146939</v>
+        <v>129147920</v>
       </c>
       <c r="B17" t="n">
-        <v>91988</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580964</v>
+        <v>581077</v>
       </c>
       <c r="R17" t="n">
-        <v>6952430</v>
+        <v>6952314</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129147920</v>
+        <v>129146939</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>91995</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581077</v>
+        <v>580964</v>
       </c>
       <c r="R18" t="n">
-        <v>6952314</v>
+        <v>6952430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,7 +2373,7 @@
         <v>129146554</v>
       </c>
       <c r="B19" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146985</v>
+        <v>129145861</v>
       </c>
       <c r="B20" t="n">
-        <v>91818</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,34 +2478,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581008</v>
+        <v>580975</v>
       </c>
       <c r="R20" t="n">
-        <v>6952388</v>
+        <v>6952488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,6 +2543,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2564,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146915</v>
+        <v>129146985</v>
       </c>
       <c r="B21" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R21" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B22" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R22" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2758,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129145861</v>
+        <v>129147319</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>91825</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,39 +2779,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580975</v>
+        <v>581032</v>
       </c>
       <c r="R23" t="n">
-        <v>6952488</v>
+        <v>6952316</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>91734</v>
+        <v>91995</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R24" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147966</v>
+        <v>129145307</v>
       </c>
       <c r="B25" t="n">
-        <v>91988</v>
+        <v>91741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581110</v>
+        <v>581027</v>
       </c>
       <c r="R25" t="n">
-        <v>6952279</v>
+        <v>6952418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,45 +3364,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B29" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R29" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,49 +3465,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>91825</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R30" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,7 +3672,7 @@
         <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B37" t="n">
-        <v>91734</v>
+        <v>91995</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R37" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B38" t="n">
-        <v>91988</v>
+        <v>91741</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R38" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92206</v>
+        <v>92213</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>129145777</v>
       </c>
       <c r="B43" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129145366</v>
       </c>
       <c r="B44" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147161</v>
+        <v>129147338</v>
       </c>
       <c r="B45" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581019</v>
+        <v>581035</v>
       </c>
       <c r="R45" t="n">
-        <v>6952367</v>
+        <v>6952297</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147111</v>
+        <v>129147161</v>
       </c>
       <c r="B46" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581035</v>
+        <v>581019</v>
       </c>
       <c r="R46" t="n">
-        <v>6952380</v>
+        <v>6952367</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129147338</v>
+        <v>129147111</v>
       </c>
       <c r="B47" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>581035</v>
       </c>
       <c r="R47" t="n">
-        <v>6952297</v>
+        <v>6952380</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5258,7 +5258,7 @@
         <v>129148498</v>
       </c>
       <c r="B48" t="n">
-        <v>92158</v>
+        <v>92165</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>129147435</v>
       </c>
       <c r="B49" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5449,45 +5449,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147878</v>
+        <v>129145829</v>
       </c>
       <c r="B50" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581069</v>
+        <v>580986</v>
       </c>
       <c r="R50" t="n">
-        <v>6952305</v>
+        <v>6952449</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5546,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147223</v>
+        <v>129147878</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5557,39 +5561,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581028</v>
+        <v>581069</v>
       </c>
       <c r="R51" t="n">
-        <v>6952359</v>
+        <v>6952305</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5622,11 +5621,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5653,37 +5647,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129145829</v>
+        <v>129147223</v>
       </c>
       <c r="B52" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580986</v>
+        <v>581028</v>
       </c>
       <c r="R52" t="n">
-        <v>6952449</v>
+        <v>6952359</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5728,6 +5723,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>129013513</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129013351</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>129013314</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>129013342</v>
       </c>
       <c r="B9" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,32 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147978</v>
+        <v>129145329</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581098</v>
+        <v>581027</v>
       </c>
       <c r="R11" t="n">
-        <v>6952295</v>
+        <v>6952418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145329</v>
+        <v>129147195</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581027</v>
+        <v>581017</v>
       </c>
       <c r="R12" t="n">
-        <v>6952418</v>
+        <v>6952357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
         <v>129145512</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147195</v>
+        <v>129147106</v>
       </c>
       <c r="B14" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581017</v>
+        <v>581035</v>
       </c>
       <c r="R14" t="n">
-        <v>6952357</v>
+        <v>6952380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147106</v>
+        <v>129147978</v>
       </c>
       <c r="B15" t="n">
-        <v>91825</v>
+        <v>91506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581035</v>
+        <v>581098</v>
       </c>
       <c r="R15" t="n">
-        <v>6952380</v>
+        <v>6952295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
         <v>129145962</v>
       </c>
       <c r="B16" t="n">
-        <v>57566</v>
+        <v>57568</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>129147920</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>129146939</v>
       </c>
       <c r="B18" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146554</v>
+        <v>129146985</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R19" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129145861</v>
+        <v>129146915</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>91827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,39 +2478,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R20" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2543,11 +2538,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2574,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146985</v>
+        <v>129147319</v>
       </c>
       <c r="B21" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581008</v>
+        <v>581032</v>
       </c>
       <c r="R21" t="n">
-        <v>6952388</v>
+        <v>6952316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2671,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146915</v>
+        <v>129146554</v>
       </c>
       <c r="B22" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2672,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129147319</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91825</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581032</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952316</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147966</v>
+        <v>129145307</v>
       </c>
       <c r="B24" t="n">
-        <v>91995</v>
+        <v>91743</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581110</v>
+        <v>581027</v>
       </c>
       <c r="R24" t="n">
-        <v>6952279</v>
+        <v>6952418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129145307</v>
+        <v>129147254</v>
       </c>
       <c r="B25" t="n">
-        <v>91741</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581027</v>
+        <v>581037</v>
       </c>
       <c r="R25" t="n">
-        <v>6952418</v>
+        <v>6952341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147254</v>
+        <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,34 +3070,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581037</v>
+        <v>580977</v>
       </c>
       <c r="R26" t="n">
-        <v>6952341</v>
+        <v>6952440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,6 +3135,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3156,50 +3166,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145834</v>
+        <v>129147966</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>91997</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580977</v>
+        <v>581110</v>
       </c>
       <c r="R27" t="n">
-        <v>6952440</v>
+        <v>6952279</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,11 +3237,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,49 +3364,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R29" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3465,45 +3461,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>91825</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R30" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3565,7 +3565,7 @@
         <v>129147381</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>129147282</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129147892</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>91995</v>
+        <v>91743</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R37" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>91741</v>
+        <v>91997</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R38" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92213</v>
+        <v>92215</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>129147998</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129145777</v>
+        <v>129147161</v>
       </c>
       <c r="B43" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580994</v>
+        <v>581019</v>
       </c>
       <c r="R43" t="n">
-        <v>6952436</v>
+        <v>6952367</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145366</v>
+        <v>129147111</v>
       </c>
       <c r="B44" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R44" t="n">
-        <v>6952419</v>
+        <v>6952380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147338</v>
+        <v>129145777</v>
       </c>
       <c r="B45" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581035</v>
+        <v>580994</v>
       </c>
       <c r="R45" t="n">
-        <v>6952297</v>
+        <v>6952436</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147161</v>
+        <v>129147338</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581019</v>
+        <v>581035</v>
       </c>
       <c r="R46" t="n">
-        <v>6952367</v>
+        <v>6952297</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129147111</v>
+        <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R47" t="n">
-        <v>6952380</v>
+        <v>6952419</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5255,45 +5255,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129148498</v>
+        <v>129147223</v>
       </c>
       <c r="B48" t="n">
-        <v>92165</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581137</v>
+        <v>581028</v>
       </c>
       <c r="R48" t="n">
-        <v>6952306</v>
+        <v>6952359</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5326,6 +5331,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5352,32 +5362,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147435</v>
+        <v>129148498</v>
       </c>
       <c r="B49" t="n">
-        <v>91825</v>
+        <v>92167</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581012</v>
+        <v>581137</v>
       </c>
       <c r="R49" t="n">
-        <v>6952237</v>
+        <v>6952306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,49 +5459,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129145829</v>
+        <v>129147878</v>
       </c>
       <c r="B50" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580986</v>
+        <v>581069</v>
       </c>
       <c r="R50" t="n">
-        <v>6952449</v>
+        <v>6952305</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,10 +5556,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147878</v>
+        <v>129147435</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5567,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581069</v>
+        <v>581012</v>
       </c>
       <c r="R51" t="n">
-        <v>6952305</v>
+        <v>6952237</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,38 +5653,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129147223</v>
+        <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5687,10 +5692,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581028</v>
+        <v>580986</v>
       </c>
       <c r="R52" t="n">
-        <v>6952359</v>
+        <v>6952449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5723,11 +5728,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1285,40 +1285,35 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013314</v>
+        <v>129013342</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1387,35 +1382,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013342</v>
+        <v>129013314</v>
       </c>
       <c r="B9" t="n">
-        <v>80175</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147195</v>
+        <v>129145512</v>
       </c>
       <c r="B12" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581017</v>
+        <v>581002</v>
       </c>
       <c r="R12" t="n">
-        <v>6952357</v>
+        <v>6952394</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145512</v>
+        <v>129147978</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>91506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581002</v>
+        <v>581098</v>
       </c>
       <c r="R13" t="n">
-        <v>6952394</v>
+        <v>6952295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147106</v>
+        <v>129147195</v>
       </c>
       <c r="B14" t="n">
         <v>91827</v>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581035</v>
+        <v>581017</v>
       </c>
       <c r="R14" t="n">
-        <v>6952380</v>
+        <v>6952357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147978</v>
+        <v>129147106</v>
       </c>
       <c r="B15" t="n">
-        <v>91506</v>
+        <v>91827</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581098</v>
+        <v>581035</v>
       </c>
       <c r="R15" t="n">
-        <v>6952295</v>
+        <v>6952380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129147920</v>
+        <v>129146939</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>91997</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581077</v>
+        <v>580964</v>
       </c>
       <c r="R17" t="n">
-        <v>6952314</v>
+        <v>6952430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129146939</v>
+        <v>129147920</v>
       </c>
       <c r="B18" t="n">
-        <v>91997</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580964</v>
+        <v>581077</v>
       </c>
       <c r="R18" t="n">
-        <v>6952430</v>
+        <v>6952314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146985</v>
+        <v>129146554</v>
       </c>
       <c r="B19" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R19" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146915</v>
+        <v>129146985</v>
       </c>
       <c r="B20" t="n">
         <v>91827</v>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R20" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B21" t="n">
         <v>91827</v>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R21" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146554</v>
+        <v>129147319</v>
       </c>
       <c r="B22" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,21 +2672,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R22" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>91743</v>
+        <v>91997</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R24" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147254</v>
+        <v>129145307</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>91743</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581037</v>
+        <v>581027</v>
       </c>
       <c r="R25" t="n">
-        <v>6952341</v>
+        <v>6952418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129145834</v>
+        <v>129147254</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,39 +3070,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580977</v>
+        <v>581037</v>
       </c>
       <c r="R26" t="n">
-        <v>6952440</v>
+        <v>6952341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,11 +3130,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3166,45 +3156,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129147966</v>
+        <v>129145834</v>
       </c>
       <c r="B27" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581110</v>
+        <v>580977</v>
       </c>
       <c r="R27" t="n">
-        <v>6952279</v>
+        <v>6952440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,6 +3232,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4566,10 +4566,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129147948</v>
+        <v>129147998</v>
       </c>
       <c r="B41" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4577,34 +4577,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581098</v>
+        <v>581110</v>
       </c>
       <c r="R41" t="n">
-        <v>6952295</v>
+        <v>6952279</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4637,6 +4642,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4663,10 +4673,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129147998</v>
+        <v>129147948</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4674,39 +4684,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581110</v>
+        <v>581098</v>
       </c>
       <c r="R42" t="n">
-        <v>6952279</v>
+        <v>6952295</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4739,11 +4744,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129147161</v>
+        <v>129145777</v>
       </c>
       <c r="B43" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581019</v>
+        <v>580994</v>
       </c>
       <c r="R43" t="n">
-        <v>6952367</v>
+        <v>6952436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129147111</v>
+        <v>129145366</v>
       </c>
       <c r="B44" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R44" t="n">
-        <v>6952380</v>
+        <v>6952419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129145777</v>
+        <v>129147161</v>
       </c>
       <c r="B45" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580994</v>
+        <v>581019</v>
       </c>
       <c r="R45" t="n">
-        <v>6952436</v>
+        <v>6952367</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147338</v>
+        <v>129147111</v>
       </c>
       <c r="B46" t="n">
         <v>91542</v>
@@ -5099,7 +5099,7 @@
         <v>581035</v>
       </c>
       <c r="R46" t="n">
-        <v>6952297</v>
+        <v>6952380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129145366</v>
+        <v>129147338</v>
       </c>
       <c r="B47" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R47" t="n">
-        <v>6952419</v>
+        <v>6952297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129147223</v>
+        <v>129147878</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,39 +5266,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581028</v>
+        <v>581069</v>
       </c>
       <c r="R48" t="n">
-        <v>6952359</v>
+        <v>6952305</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5331,11 +5326,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5459,10 +5449,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147878</v>
+        <v>129147435</v>
       </c>
       <c r="B50" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,21 +5460,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5484,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581069</v>
+        <v>581012</v>
       </c>
       <c r="R50" t="n">
-        <v>6952305</v>
+        <v>6952237</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5556,10 +5546,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147435</v>
+        <v>129147223</v>
       </c>
       <c r="B51" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,34 +5557,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581012</v>
+        <v>581028</v>
       </c>
       <c r="R51" t="n">
-        <v>6952237</v>
+        <v>6952359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,6 +5622,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146554</v>
+        <v>129145861</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,34 +2381,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R19" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,6 +2446,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2758,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129145861</v>
+        <v>129146554</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,39 +2779,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R23" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4566,10 +4566,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129147998</v>
+        <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4577,39 +4577,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581110</v>
+        <v>581098</v>
       </c>
       <c r="R41" t="n">
-        <v>6952279</v>
+        <v>6952295</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,11 +4637,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4673,10 +4663,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129147948</v>
+        <v>129147998</v>
       </c>
       <c r="B42" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4684,34 +4674,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581098</v>
+        <v>581110</v>
       </c>
       <c r="R42" t="n">
-        <v>6952295</v>
+        <v>6952279</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4744,6 +4739,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129145777</v>
+        <v>129147161</v>
       </c>
       <c r="B43" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580994</v>
+        <v>581019</v>
       </c>
       <c r="R43" t="n">
-        <v>6952436</v>
+        <v>6952367</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145366</v>
+        <v>129147111</v>
       </c>
       <c r="B44" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R44" t="n">
-        <v>6952419</v>
+        <v>6952380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147161</v>
+        <v>129147338</v>
       </c>
       <c r="B45" t="n">
         <v>91542</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581019</v>
+        <v>581035</v>
       </c>
       <c r="R45" t="n">
-        <v>6952367</v>
+        <v>6952297</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147111</v>
+        <v>129145777</v>
       </c>
       <c r="B46" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581035</v>
+        <v>580994</v>
       </c>
       <c r="R46" t="n">
-        <v>6952380</v>
+        <v>6952436</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129147338</v>
+        <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R47" t="n">
-        <v>6952297</v>
+        <v>6952419</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>129145329</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145512</v>
+        <v>129147195</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581002</v>
+        <v>581017</v>
       </c>
       <c r="R12" t="n">
-        <v>6952394</v>
+        <v>6952357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147978</v>
+        <v>129147106</v>
       </c>
       <c r="B13" t="n">
-        <v>91506</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581098</v>
+        <v>581035</v>
       </c>
       <c r="R13" t="n">
-        <v>6952295</v>
+        <v>6952380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147195</v>
+        <v>129145512</v>
       </c>
       <c r="B14" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581017</v>
+        <v>581002</v>
       </c>
       <c r="R14" t="n">
-        <v>6952357</v>
+        <v>6952394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147106</v>
+        <v>129147978</v>
       </c>
       <c r="B15" t="n">
-        <v>91827</v>
+        <v>91504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581035</v>
+        <v>581098</v>
       </c>
       <c r="R15" t="n">
-        <v>6952380</v>
+        <v>6952295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
         <v>129146939</v>
       </c>
       <c r="B17" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,12 +2196,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129145861</v>
+        <v>129146985</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>91837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,39 +2381,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580975</v>
+        <v>581008</v>
       </c>
       <c r="R19" t="n">
-        <v>6952488</v>
+        <v>6952388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,11 +2441,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2477,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146985</v>
+        <v>129146554</v>
       </c>
       <c r="B20" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R20" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146915</v>
+        <v>129147319</v>
       </c>
       <c r="B21" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R21" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2671,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B22" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,10 +2696,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R22" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146554</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147966</v>
+        <v>129145307</v>
       </c>
       <c r="B24" t="n">
-        <v>91997</v>
+        <v>91752</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581110</v>
+        <v>581027</v>
       </c>
       <c r="R24" t="n">
-        <v>6952279</v>
+        <v>6952418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B25" t="n">
-        <v>91743</v>
+        <v>91992</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R25" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,45 +3364,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B29" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R29" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,49 +3465,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R30" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B32" t="n">
-        <v>91997</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R32" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B33" t="n">
-        <v>91542</v>
+        <v>91992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R33" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B37" t="n">
-        <v>91743</v>
+        <v>91992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R37" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B38" t="n">
-        <v>91997</v>
+        <v>91752</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R38" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92215</v>
+        <v>92230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129147161</v>
+        <v>129147338</v>
       </c>
       <c r="B43" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581019</v>
+        <v>581035</v>
       </c>
       <c r="R43" t="n">
-        <v>6952367</v>
+        <v>6952297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129147111</v>
+        <v>129147161</v>
       </c>
       <c r="B44" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581035</v>
+        <v>581019</v>
       </c>
       <c r="R44" t="n">
-        <v>6952380</v>
+        <v>6952367</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147338</v>
+        <v>129147111</v>
       </c>
       <c r="B45" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>581035</v>
       </c>
       <c r="R45" t="n">
-        <v>6952297</v>
+        <v>6952380</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5064,7 +5064,7 @@
         <v>129145777</v>
       </c>
       <c r="B46" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129147878</v>
+        <v>129147435</v>
       </c>
       <c r="B48" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,21 +5266,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581069</v>
+        <v>581012</v>
       </c>
       <c r="R48" t="n">
-        <v>6952305</v>
+        <v>6952237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5352,32 +5352,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129148498</v>
+        <v>129147878</v>
       </c>
       <c r="B49" t="n">
-        <v>92167</v>
+        <v>91540</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>483</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581137</v>
+        <v>581069</v>
       </c>
       <c r="R49" t="n">
-        <v>6952306</v>
+        <v>6952305</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,32 +5449,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147435</v>
+        <v>129148498</v>
       </c>
       <c r="B50" t="n">
-        <v>91827</v>
+        <v>92182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581012</v>
+        <v>581137</v>
       </c>
       <c r="R50" t="n">
-        <v>6952237</v>
+        <v>6952306</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5656,7 +5656,7 @@
         <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,35 +1285,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013342</v>
+        <v>129013314</v>
       </c>
       <c r="B8" t="n">
-        <v>80175</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1382,40 +1387,35 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013314</v>
+        <v>129013342</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1487,7 +1487,7 @@
         <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,45 +1585,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145329</v>
+        <v>129145962</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>57568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581027</v>
+        <v>580975</v>
       </c>
       <c r="R11" t="n">
-        <v>6952418</v>
+        <v>6952488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,32 +1691,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147195</v>
+        <v>129147978</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>91504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581017</v>
+        <v>581098</v>
       </c>
       <c r="R12" t="n">
-        <v>6952357</v>
+        <v>6952295</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147106</v>
+        <v>129147195</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581035</v>
+        <v>581017</v>
       </c>
       <c r="R13" t="n">
-        <v>6952380</v>
+        <v>6952357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129145512</v>
+        <v>129147106</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581002</v>
+        <v>581035</v>
       </c>
       <c r="R14" t="n">
-        <v>6952394</v>
+        <v>6952380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147978</v>
+        <v>129145329</v>
       </c>
       <c r="B15" t="n">
-        <v>91504</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581098</v>
+        <v>581027</v>
       </c>
       <c r="R15" t="n">
-        <v>6952295</v>
+        <v>6952418</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,54 +2079,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129145962</v>
+        <v>129145512</v>
       </c>
       <c r="B16" t="n">
-        <v>57568</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580975</v>
+        <v>581002</v>
       </c>
       <c r="R16" t="n">
-        <v>6952488</v>
+        <v>6952394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
         <v>129146939</v>
       </c>
       <c r="B17" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146985</v>
+        <v>129146915</v>
       </c>
       <c r="B19" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R19" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146554</v>
+        <v>129147319</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R20" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129147319</v>
+        <v>129145861</v>
       </c>
       <c r="B21" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,34 +2575,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581032</v>
+        <v>580975</v>
       </c>
       <c r="R21" t="n">
-        <v>6952316</v>
+        <v>6952488</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2635,6 +2640,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2661,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146915</v>
+        <v>129146985</v>
       </c>
       <c r="B22" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R22" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2758,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129145861</v>
+        <v>129146554</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,39 +2779,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R23" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>91752</v>
+        <v>91993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R24" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147966</v>
+        <v>129147254</v>
       </c>
       <c r="B25" t="n">
-        <v>91992</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581110</v>
+        <v>581037</v>
       </c>
       <c r="R25" t="n">
-        <v>6952279</v>
+        <v>6952341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147254</v>
+        <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,34 +3070,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581037</v>
+        <v>580977</v>
       </c>
       <c r="R26" t="n">
-        <v>6952341</v>
+        <v>6952440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,6 +3135,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3156,50 +3166,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145834</v>
+        <v>129145307</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>91753</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580977</v>
+        <v>581027</v>
       </c>
       <c r="R27" t="n">
-        <v>6952440</v>
+        <v>6952418</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,11 +3237,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,49 +3364,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R29" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3465,45 +3461,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R30" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91993</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R32" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91992</v>
+        <v>91540</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R33" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>91992</v>
+        <v>91753</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R37" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>91752</v>
+        <v>91993</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R38" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92230</v>
+        <v>92231</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129147338</v>
+        <v>129145777</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581035</v>
+        <v>580994</v>
       </c>
       <c r="R43" t="n">
-        <v>6952297</v>
+        <v>6952436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129147161</v>
+        <v>129145366</v>
       </c>
       <c r="B44" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581019</v>
+        <v>581021</v>
       </c>
       <c r="R44" t="n">
-        <v>6952367</v>
+        <v>6952419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147111</v>
+        <v>129147161</v>
       </c>
       <c r="B45" t="n">
         <v>91540</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581035</v>
+        <v>581019</v>
       </c>
       <c r="R45" t="n">
-        <v>6952380</v>
+        <v>6952367</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129145777</v>
+        <v>129147111</v>
       </c>
       <c r="B46" t="n">
-        <v>91837</v>
+        <v>91540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580994</v>
+        <v>581035</v>
       </c>
       <c r="R46" t="n">
-        <v>6952436</v>
+        <v>6952380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129145366</v>
+        <v>129147338</v>
       </c>
       <c r="B47" t="n">
-        <v>91837</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R47" t="n">
-        <v>6952419</v>
+        <v>6952297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129147435</v>
+        <v>129147223</v>
       </c>
       <c r="B48" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,34 +5266,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581012</v>
+        <v>581028</v>
       </c>
       <c r="R48" t="n">
-        <v>6952237</v>
+        <v>6952359</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5326,6 +5331,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5352,32 +5362,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147878</v>
+        <v>129148498</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>92183</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>483</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581069</v>
+        <v>581137</v>
       </c>
       <c r="R49" t="n">
-        <v>6952305</v>
+        <v>6952306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,32 +5459,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129148498</v>
+        <v>129147435</v>
       </c>
       <c r="B50" t="n">
-        <v>92182</v>
+        <v>91838</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5484,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581137</v>
+        <v>581012</v>
       </c>
       <c r="R50" t="n">
-        <v>6952306</v>
+        <v>6952237</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5546,10 +5556,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147223</v>
+        <v>129147878</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5557,39 +5567,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581028</v>
+        <v>581069</v>
       </c>
       <c r="R51" t="n">
-        <v>6952359</v>
+        <v>6952305</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5622,11 +5627,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5656,7 +5656,7 @@
         <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1387,45 +1387,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013342</v>
+        <v>129013448</v>
       </c>
       <c r="B9" t="n">
-        <v>80175</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R9" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,49 +1488,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013448</v>
+        <v>129013342</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>80175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R10" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147195</v>
+        <v>129145329</v>
       </c>
       <c r="B13" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581017</v>
+        <v>581027</v>
       </c>
       <c r="R13" t="n">
-        <v>6952357</v>
+        <v>6952418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147106</v>
+        <v>129147195</v>
       </c>
       <c r="B14" t="n">
         <v>91838</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581035</v>
+        <v>581017</v>
       </c>
       <c r="R14" t="n">
-        <v>6952380</v>
+        <v>6952357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129145329</v>
+        <v>129145512</v>
       </c>
       <c r="B15" t="n">
         <v>91540</v>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581027</v>
+        <v>581002</v>
       </c>
       <c r="R15" t="n">
-        <v>6952418</v>
+        <v>6952394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129145512</v>
+        <v>129147106</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581002</v>
+        <v>581035</v>
       </c>
       <c r="R16" t="n">
-        <v>6952394</v>
+        <v>6952380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129146939</v>
+        <v>129147920</v>
       </c>
       <c r="B17" t="n">
-        <v>91993</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580964</v>
+        <v>581077</v>
       </c>
       <c r="R17" t="n">
-        <v>6952430</v>
+        <v>6952314</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129147920</v>
+        <v>129146939</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>91993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581077</v>
+        <v>580964</v>
       </c>
       <c r="R18" t="n">
-        <v>6952314</v>
+        <v>6952430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146915</v>
+        <v>129146985</v>
       </c>
       <c r="B19" t="n">
         <v>91838</v>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R19" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B20" t="n">
         <v>91838</v>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R20" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129145861</v>
+        <v>129147319</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,39 +2575,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580975</v>
+        <v>581032</v>
       </c>
       <c r="R21" t="n">
-        <v>6952488</v>
+        <v>6952316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2640,11 +2635,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2671,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146985</v>
+        <v>129146554</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2672,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2696,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R22" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146554</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147966</v>
+        <v>129145307</v>
       </c>
       <c r="B24" t="n">
-        <v>91993</v>
+        <v>91753</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581110</v>
+        <v>581027</v>
       </c>
       <c r="R24" t="n">
-        <v>6952279</v>
+        <v>6952418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147254</v>
+        <v>129147966</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>91993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581037</v>
+        <v>581110</v>
       </c>
       <c r="R25" t="n">
-        <v>6952341</v>
+        <v>6952279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129145834</v>
+        <v>129147254</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,39 +3070,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580977</v>
+        <v>581037</v>
       </c>
       <c r="R26" t="n">
-        <v>6952440</v>
+        <v>6952341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,11 +3130,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3166,45 +3156,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145307</v>
+        <v>129145834</v>
       </c>
       <c r="B27" t="n">
-        <v>91753</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581027</v>
+        <v>580977</v>
       </c>
       <c r="R27" t="n">
-        <v>6952418</v>
+        <v>6952440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,6 +3232,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129145777</v>
+        <v>129147161</v>
       </c>
       <c r="B43" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580994</v>
+        <v>581019</v>
       </c>
       <c r="R43" t="n">
-        <v>6952436</v>
+        <v>6952367</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145366</v>
+        <v>129147111</v>
       </c>
       <c r="B44" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R44" t="n">
-        <v>6952419</v>
+        <v>6952380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147161</v>
+        <v>129145777</v>
       </c>
       <c r="B45" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581019</v>
+        <v>580994</v>
       </c>
       <c r="R45" t="n">
-        <v>6952367</v>
+        <v>6952436</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147111</v>
+        <v>129147338</v>
       </c>
       <c r="B46" t="n">
         <v>91540</v>
@@ -5099,7 +5099,7 @@
         <v>581035</v>
       </c>
       <c r="R46" t="n">
-        <v>6952380</v>
+        <v>6952297</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129147338</v>
+        <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R47" t="n">
-        <v>6952297</v>
+        <v>6952419</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5255,38 +5255,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129147223</v>
+        <v>129145829</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5295,10 +5294,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581028</v>
+        <v>580986</v>
       </c>
       <c r="R48" t="n">
-        <v>6952359</v>
+        <v>6952449</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5331,11 +5330,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5362,32 +5356,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129148498</v>
+        <v>129147878</v>
       </c>
       <c r="B49" t="n">
-        <v>92183</v>
+        <v>91540</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>483</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5397,10 +5391,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581137</v>
+        <v>581069</v>
       </c>
       <c r="R49" t="n">
-        <v>6952306</v>
+        <v>6952305</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5556,32 +5550,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147878</v>
+        <v>129148498</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>92183</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>483</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581069</v>
+        <v>581137</v>
       </c>
       <c r="R51" t="n">
-        <v>6952305</v>
+        <v>6952306</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5653,37 +5647,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129145829</v>
+        <v>129147223</v>
       </c>
       <c r="B52" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580986</v>
+        <v>581028</v>
       </c>
       <c r="R52" t="n">
-        <v>6952449</v>
+        <v>6952359</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5728,6 +5723,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,38 +1285,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013314</v>
+        <v>129013448</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1325,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R8" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,49 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013448</v>
+        <v>129013342</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>80177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R9" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,35 +1483,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013342</v>
+        <v>129013314</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>80148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1585,54 +1585,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145962</v>
+        <v>129145329</v>
       </c>
       <c r="B11" t="n">
-        <v>57568</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580975</v>
+        <v>581027</v>
       </c>
       <c r="R11" t="n">
-        <v>6952488</v>
+        <v>6952418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147978</v>
+        <v>129145512</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581098</v>
+        <v>581002</v>
       </c>
       <c r="R12" t="n">
-        <v>6952295</v>
+        <v>6952394</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145329</v>
+        <v>129147195</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581027</v>
+        <v>581017</v>
       </c>
       <c r="R13" t="n">
-        <v>6952418</v>
+        <v>6952357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147195</v>
+        <v>129147106</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581017</v>
+        <v>581035</v>
       </c>
       <c r="R14" t="n">
-        <v>6952357</v>
+        <v>6952380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129145512</v>
+        <v>129147978</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581002</v>
+        <v>581098</v>
       </c>
       <c r="R15" t="n">
-        <v>6952394</v>
+        <v>6952295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,45 +2070,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129147106</v>
+        <v>129145962</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>57568</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>102621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581035</v>
+        <v>580975</v>
       </c>
       <c r="R16" t="n">
-        <v>6952380</v>
+        <v>6952488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129147920</v>
+        <v>129146939</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>91996</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581077</v>
+        <v>580964</v>
       </c>
       <c r="R17" t="n">
-        <v>6952314</v>
+        <v>6952430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129146939</v>
+        <v>129147920</v>
       </c>
       <c r="B18" t="n">
-        <v>91993</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580964</v>
+        <v>581077</v>
       </c>
       <c r="R18" t="n">
-        <v>6952430</v>
+        <v>6952314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146985</v>
+        <v>129146554</v>
       </c>
       <c r="B19" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R19" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146915</v>
+        <v>129146985</v>
       </c>
       <c r="B20" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R20" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B21" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R21" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146554</v>
+        <v>129147319</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,21 +2672,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R22" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2868,7 +2868,7 @@
         <v>129145307</v>
       </c>
       <c r="B24" t="n">
-        <v>91753</v>
+        <v>91756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129147966</v>
       </c>
       <c r="B25" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129147254</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>91753</v>
+        <v>91756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92231</v>
+        <v>92234</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>129147161</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129147111</v>
       </c>
       <c r="B44" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129145777</v>
+        <v>129147338</v>
       </c>
       <c r="B45" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580994</v>
+        <v>581035</v>
       </c>
       <c r="R45" t="n">
-        <v>6952436</v>
+        <v>6952297</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147338</v>
+        <v>129145777</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581035</v>
+        <v>580994</v>
       </c>
       <c r="R46" t="n">
-        <v>6952297</v>
+        <v>6952436</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5161,7 +5161,7 @@
         <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5255,49 +5255,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129145829</v>
+        <v>129147878</v>
       </c>
       <c r="B48" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580986</v>
+        <v>581069</v>
       </c>
       <c r="R48" t="n">
-        <v>6952449</v>
+        <v>6952305</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5356,32 +5352,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147878</v>
+        <v>129148498</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>92186</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>483</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5391,10 +5387,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581069</v>
+        <v>581137</v>
       </c>
       <c r="R49" t="n">
-        <v>6952305</v>
+        <v>6952306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5456,7 +5452,7 @@
         <v>129147435</v>
       </c>
       <c r="B50" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5550,45 +5546,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129148498</v>
+        <v>129147223</v>
       </c>
       <c r="B51" t="n">
-        <v>92183</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>483</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581137</v>
+        <v>581028</v>
       </c>
       <c r="R51" t="n">
-        <v>6952306</v>
+        <v>6952359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5621,6 +5622,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5647,38 +5653,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129147223</v>
+        <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5687,10 +5692,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581028</v>
+        <v>580986</v>
       </c>
       <c r="R52" t="n">
-        <v>6952359</v>
+        <v>6952449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5723,11 +5728,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1285,49 +1285,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013448</v>
+        <v>129013342</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>80177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R8" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,35 +1382,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013342</v>
+        <v>129013314</v>
       </c>
       <c r="B9" t="n">
-        <v>80177</v>
+        <v>80148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1483,38 +1484,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013314</v>
+        <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R10" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145329</v>
+        <v>129147106</v>
       </c>
       <c r="B11" t="n">
-        <v>91543</v>
+        <v>91841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581027</v>
+        <v>581035</v>
       </c>
       <c r="R11" t="n">
-        <v>6952418</v>
+        <v>6952380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145512</v>
+        <v>129147978</v>
       </c>
       <c r="B12" t="n">
-        <v>91543</v>
+        <v>91507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581002</v>
+        <v>581098</v>
       </c>
       <c r="R12" t="n">
-        <v>6952394</v>
+        <v>6952295</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147195</v>
+        <v>129145329</v>
       </c>
       <c r="B13" t="n">
-        <v>91841</v>
+        <v>91543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581017</v>
+        <v>581027</v>
       </c>
       <c r="R13" t="n">
-        <v>6952357</v>
+        <v>6952418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147106</v>
+        <v>129145512</v>
       </c>
       <c r="B14" t="n">
-        <v>91841</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581035</v>
+        <v>581002</v>
       </c>
       <c r="R14" t="n">
-        <v>6952380</v>
+        <v>6952394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147978</v>
+        <v>129147195</v>
       </c>
       <c r="B15" t="n">
-        <v>91507</v>
+        <v>91841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581098</v>
+        <v>581017</v>
       </c>
       <c r="R15" t="n">
-        <v>6952295</v>
+        <v>6952357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>91756</v>
+        <v>91996</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R24" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147966</v>
+        <v>129145307</v>
       </c>
       <c r="B25" t="n">
-        <v>91996</v>
+        <v>91756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581110</v>
+        <v>581027</v>
       </c>
       <c r="R25" t="n">
-        <v>6952279</v>
+        <v>6952418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147254</v>
+        <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,34 +3070,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581037</v>
+        <v>580977</v>
       </c>
       <c r="R26" t="n">
-        <v>6952341</v>
+        <v>6952440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,6 +3135,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3156,10 +3166,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145834</v>
+        <v>129147254</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,39 +3177,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580977</v>
+        <v>581037</v>
       </c>
       <c r="R27" t="n">
-        <v>6952440</v>
+        <v>6952341</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,11 +3237,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5255,10 +5255,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129147878</v>
+        <v>129147223</v>
       </c>
       <c r="B48" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,34 +5266,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581069</v>
+        <v>581028</v>
       </c>
       <c r="R48" t="n">
-        <v>6952305</v>
+        <v>6952359</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5326,6 +5331,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5352,32 +5362,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129148498</v>
+        <v>129147878</v>
       </c>
       <c r="B49" t="n">
-        <v>92186</v>
+        <v>91543</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>483</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581137</v>
+        <v>581069</v>
       </c>
       <c r="R49" t="n">
-        <v>6952306</v>
+        <v>6952305</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,45 +5459,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147435</v>
+        <v>129145829</v>
       </c>
       <c r="B50" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581012</v>
+        <v>580986</v>
       </c>
       <c r="R50" t="n">
-        <v>6952237</v>
+        <v>6952449</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5546,50 +5560,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147223</v>
+        <v>129148498</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>92186</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>483</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581028</v>
+        <v>581137</v>
       </c>
       <c r="R51" t="n">
-        <v>6952359</v>
+        <v>6952306</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5622,11 +5631,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5653,49 +5657,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129145829</v>
+        <v>129147435</v>
       </c>
       <c r="B52" t="n">
-        <v>98710</v>
+        <v>91841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580986</v>
+        <v>581012</v>
       </c>
       <c r="R52" t="n">
-        <v>6952449</v>
+        <v>6952237</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,45 +1285,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013342</v>
+        <v>129013448</v>
       </c>
       <c r="B8" t="n">
-        <v>80177</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R8" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,40 +1386,35 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013314</v>
+        <v>129013342</v>
       </c>
       <c r="B9" t="n">
-        <v>80148</v>
+        <v>80178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1484,37 +1483,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013448</v>
+        <v>129013314</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R10" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147106</v>
+        <v>129145329</v>
       </c>
       <c r="B11" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581035</v>
+        <v>581027</v>
       </c>
       <c r="R11" t="n">
-        <v>6952380</v>
+        <v>6952418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147978</v>
+        <v>129145512</v>
       </c>
       <c r="B12" t="n">
-        <v>91507</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581098</v>
+        <v>581002</v>
       </c>
       <c r="R12" t="n">
-        <v>6952295</v>
+        <v>6952394</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145329</v>
+        <v>129147978</v>
       </c>
       <c r="B13" t="n">
-        <v>91543</v>
+        <v>91509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581027</v>
+        <v>581098</v>
       </c>
       <c r="R13" t="n">
-        <v>6952418</v>
+        <v>6952295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,45 +1876,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129145512</v>
+        <v>129145962</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>57568</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581002</v>
+        <v>580975</v>
       </c>
       <c r="R14" t="n">
-        <v>6952394</v>
+        <v>6952488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,7 +1985,7 @@
         <v>129147195</v>
       </c>
       <c r="B15" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,54 +2079,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129145962</v>
+        <v>129147106</v>
       </c>
       <c r="B16" t="n">
-        <v>57568</v>
+        <v>91843</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102621</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580975</v>
+        <v>581035</v>
       </c>
       <c r="R16" t="n">
-        <v>6952488</v>
+        <v>6952380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
         <v>129146939</v>
       </c>
       <c r="B17" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>129147920</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146554</v>
+        <v>129146985</v>
       </c>
       <c r="B19" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R19" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146985</v>
+        <v>129146915</v>
       </c>
       <c r="B20" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R20" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146915</v>
+        <v>129147319</v>
       </c>
       <c r="B21" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R21" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129147319</v>
+        <v>129145861</v>
       </c>
       <c r="B22" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,34 +2672,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581032</v>
+        <v>580975</v>
       </c>
       <c r="R22" t="n">
-        <v>6952316</v>
+        <v>6952488</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,6 +2737,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2758,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129145861</v>
+        <v>129146554</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,39 +2779,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R23" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,45 +2865,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147966</v>
+        <v>129145834</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581110</v>
+        <v>580977</v>
       </c>
       <c r="R24" t="n">
-        <v>6952279</v>
+        <v>6952440</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,6 +2941,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2965,7 +2975,7 @@
         <v>129145307</v>
       </c>
       <c r="B25" t="n">
-        <v>91756</v>
+        <v>91758</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3059,50 +3069,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129145834</v>
+        <v>129147966</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>91998</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580977</v>
+        <v>581110</v>
       </c>
       <c r="R26" t="n">
-        <v>6952440</v>
+        <v>6952279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,11 +3140,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3169,7 +3169,7 @@
         <v>129147254</v>
       </c>
       <c r="B27" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>91756</v>
+        <v>91758</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92234</v>
+        <v>92236</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129147161</v>
+        <v>129145777</v>
       </c>
       <c r="B43" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581019</v>
+        <v>580994</v>
       </c>
       <c r="R43" t="n">
-        <v>6952367</v>
+        <v>6952436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129147111</v>
+        <v>129145366</v>
       </c>
       <c r="B44" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R44" t="n">
-        <v>6952380</v>
+        <v>6952419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147338</v>
+        <v>129147161</v>
       </c>
       <c r="B45" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581035</v>
+        <v>581019</v>
       </c>
       <c r="R45" t="n">
-        <v>6952297</v>
+        <v>6952367</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129145777</v>
+        <v>129147111</v>
       </c>
       <c r="B46" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580994</v>
+        <v>581035</v>
       </c>
       <c r="R46" t="n">
-        <v>6952436</v>
+        <v>6952380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129145366</v>
+        <v>129147338</v>
       </c>
       <c r="B47" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R47" t="n">
-        <v>6952419</v>
+        <v>6952297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5362,32 +5362,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147878</v>
+        <v>129148498</v>
       </c>
       <c r="B49" t="n">
-        <v>91543</v>
+        <v>92188</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>483</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581069</v>
+        <v>581137</v>
       </c>
       <c r="R49" t="n">
-        <v>6952305</v>
+        <v>6952306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,49 +5459,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129145829</v>
+        <v>129147435</v>
       </c>
       <c r="B50" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580986</v>
+        <v>581012</v>
       </c>
       <c r="R50" t="n">
-        <v>6952449</v>
+        <v>6952237</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5560,32 +5556,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129148498</v>
+        <v>129147878</v>
       </c>
       <c r="B51" t="n">
-        <v>92186</v>
+        <v>91545</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>483</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5595,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581137</v>
+        <v>581069</v>
       </c>
       <c r="R51" t="n">
-        <v>6952306</v>
+        <v>6952305</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5657,45 +5653,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129147435</v>
+        <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581012</v>
+        <v>580986</v>
       </c>
       <c r="R52" t="n">
-        <v>6952237</v>
+        <v>6952449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>129013448</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,32 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145329</v>
+        <v>129147978</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581027</v>
+        <v>581098</v>
       </c>
       <c r="R11" t="n">
-        <v>6952418</v>
+        <v>6952295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,45 +1682,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145512</v>
+        <v>129145962</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>57568</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581002</v>
+        <v>580975</v>
       </c>
       <c r="R12" t="n">
-        <v>6952394</v>
+        <v>6952488</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1788,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147978</v>
+        <v>129147195</v>
       </c>
       <c r="B13" t="n">
-        <v>91509</v>
+        <v>91847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581098</v>
+        <v>581017</v>
       </c>
       <c r="R13" t="n">
-        <v>6952295</v>
+        <v>6952357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,54 +1885,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129145962</v>
+        <v>129147106</v>
       </c>
       <c r="B14" t="n">
-        <v>57568</v>
+        <v>91847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580975</v>
+        <v>581035</v>
       </c>
       <c r="R14" t="n">
-        <v>6952488</v>
+        <v>6952380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147195</v>
+        <v>129145329</v>
       </c>
       <c r="B15" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581017</v>
+        <v>581027</v>
       </c>
       <c r="R15" t="n">
-        <v>6952357</v>
+        <v>6952418</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129147106</v>
+        <v>129145512</v>
       </c>
       <c r="B16" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581035</v>
+        <v>581002</v>
       </c>
       <c r="R16" t="n">
-        <v>6952380</v>
+        <v>6952394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129146939</v>
+        <v>129147920</v>
       </c>
       <c r="B17" t="n">
-        <v>91998</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580964</v>
+        <v>581077</v>
       </c>
       <c r="R17" t="n">
-        <v>6952430</v>
+        <v>6952314</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129147920</v>
+        <v>129146939</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>92002</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581077</v>
+        <v>580964</v>
       </c>
       <c r="R18" t="n">
-        <v>6952314</v>
+        <v>6952430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,7 +2373,7 @@
         <v>129146985</v>
       </c>
       <c r="B19" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>129146915</v>
       </c>
       <c r="B20" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>129147319</v>
       </c>
       <c r="B21" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129145861</v>
+        <v>129146554</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,39 +2672,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R22" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,11 +2732,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146554</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,50 +2865,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145834</v>
+        <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>92002</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580977</v>
+        <v>581110</v>
       </c>
       <c r="R24" t="n">
-        <v>6952440</v>
+        <v>6952279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,11 +2936,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2972,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129145307</v>
+        <v>129147254</v>
       </c>
       <c r="B25" t="n">
-        <v>91758</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3007,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581027</v>
+        <v>581037</v>
       </c>
       <c r="R25" t="n">
-        <v>6952418</v>
+        <v>6952341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,45 +3059,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147966</v>
+        <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>91998</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581110</v>
+        <v>580977</v>
       </c>
       <c r="R26" t="n">
-        <v>6952279</v>
+        <v>6952440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,6 +3135,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3166,32 +3166,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129147254</v>
+        <v>129145307</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>91762</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581037</v>
+        <v>581027</v>
       </c>
       <c r="R27" t="n">
-        <v>6952341</v>
+        <v>6952418</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B37" t="n">
-        <v>91758</v>
+        <v>92002</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R37" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B38" t="n">
-        <v>91998</v>
+        <v>91762</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R38" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92236</v>
+        <v>92240</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>129145777</v>
       </c>
       <c r="B43" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129145366</v>
       </c>
       <c r="B44" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>129147161</v>
       </c>
       <c r="B45" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>129147111</v>
       </c>
       <c r="B46" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>129147338</v>
       </c>
       <c r="B47" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5255,50 +5255,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129147223</v>
+        <v>129148498</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>92192</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581028</v>
+        <v>581137</v>
       </c>
       <c r="R48" t="n">
-        <v>6952359</v>
+        <v>6952306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5331,11 +5326,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5362,32 +5352,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129148498</v>
+        <v>129147435</v>
       </c>
       <c r="B49" t="n">
-        <v>92188</v>
+        <v>91847</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5397,10 +5387,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581137</v>
+        <v>581012</v>
       </c>
       <c r="R49" t="n">
-        <v>6952306</v>
+        <v>6952237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,10 +5449,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147435</v>
+        <v>129147878</v>
       </c>
       <c r="B50" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,21 +5460,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5484,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581012</v>
+        <v>581069</v>
       </c>
       <c r="R50" t="n">
-        <v>6952237</v>
+        <v>6952305</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5556,10 +5546,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147878</v>
+        <v>129147223</v>
       </c>
       <c r="B51" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,34 +5557,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581069</v>
+        <v>581028</v>
       </c>
       <c r="R51" t="n">
-        <v>6952305</v>
+        <v>6952359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,6 +5622,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5656,7 +5656,7 @@
         <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,49 +1285,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013448</v>
+        <v>129013342</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>80178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R8" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,35 +1382,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013342</v>
+        <v>129013314</v>
       </c>
       <c r="B9" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
@@ -1483,38 +1484,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013314</v>
+        <v>129013448</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R10" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,32 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147978</v>
+        <v>129145329</v>
       </c>
       <c r="B11" t="n">
-        <v>91513</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581098</v>
+        <v>581027</v>
       </c>
       <c r="R11" t="n">
-        <v>6952295</v>
+        <v>6952418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,54 +1682,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145962</v>
+        <v>129147195</v>
       </c>
       <c r="B12" t="n">
-        <v>57568</v>
+        <v>91848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580975</v>
+        <v>581017</v>
       </c>
       <c r="R12" t="n">
-        <v>6952488</v>
+        <v>6952357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147195</v>
+        <v>129145512</v>
       </c>
       <c r="B13" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581017</v>
+        <v>581002</v>
       </c>
       <c r="R13" t="n">
-        <v>6952357</v>
+        <v>6952394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,7 +1879,7 @@
         <v>129147106</v>
       </c>
       <c r="B14" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129145329</v>
+        <v>129147978</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>91514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581027</v>
+        <v>581098</v>
       </c>
       <c r="R15" t="n">
-        <v>6952418</v>
+        <v>6952295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,45 +2070,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129145512</v>
+        <v>129145962</v>
       </c>
       <c r="B16" t="n">
-        <v>91549</v>
+        <v>57568</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581002</v>
+        <v>580975</v>
       </c>
       <c r="R16" t="n">
-        <v>6952394</v>
+        <v>6952488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2276,7 +2276,7 @@
         <v>129146939</v>
       </c>
       <c r="B18" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146985</v>
+        <v>129145861</v>
       </c>
       <c r="B19" t="n">
-        <v>91847</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,34 +2381,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581008</v>
+        <v>580975</v>
       </c>
       <c r="R19" t="n">
-        <v>6952388</v>
+        <v>6952488</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,6 +2446,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2467,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146915</v>
+        <v>129146554</v>
       </c>
       <c r="B20" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2488,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129147319</v>
+        <v>129146985</v>
       </c>
       <c r="B21" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581032</v>
+        <v>581008</v>
       </c>
       <c r="R21" t="n">
-        <v>6952316</v>
+        <v>6952388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146554</v>
+        <v>129146915</v>
       </c>
       <c r="B22" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2758,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129145861</v>
+        <v>129147319</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,39 +2779,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580975</v>
+        <v>581032</v>
       </c>
       <c r="R23" t="n">
-        <v>6952488</v>
+        <v>6952316</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,32 +2865,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147966</v>
+        <v>129147254</v>
       </c>
       <c r="B24" t="n">
-        <v>92002</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581110</v>
+        <v>581037</v>
       </c>
       <c r="R24" t="n">
-        <v>6952279</v>
+        <v>6952341</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147254</v>
+        <v>129145834</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,34 +2973,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581037</v>
+        <v>580977</v>
       </c>
       <c r="R25" t="n">
-        <v>6952341</v>
+        <v>6952440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,6 +3038,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3059,50 +3069,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129145834</v>
+        <v>129147966</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>92003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580977</v>
+        <v>581110</v>
       </c>
       <c r="R26" t="n">
-        <v>6952440</v>
+        <v>6952279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,11 +3140,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3169,7 +3169,7 @@
         <v>129145307</v>
       </c>
       <c r="B27" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,45 +3364,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B29" t="n">
-        <v>91847</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R29" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,49 +3465,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B30" t="n">
-        <v>98716</v>
+        <v>91848</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R30" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,7 +3672,7 @@
         <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129145405</v>
       </c>
       <c r="B37" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129148349</v>
       </c>
       <c r="B38" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129145777</v>
+        <v>129147161</v>
       </c>
       <c r="B43" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580994</v>
+        <v>581019</v>
       </c>
       <c r="R43" t="n">
-        <v>6952436</v>
+        <v>6952367</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145366</v>
+        <v>129147111</v>
       </c>
       <c r="B44" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R44" t="n">
-        <v>6952419</v>
+        <v>6952380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147161</v>
+        <v>129147338</v>
       </c>
       <c r="B45" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581019</v>
+        <v>581035</v>
       </c>
       <c r="R45" t="n">
-        <v>6952367</v>
+        <v>6952297</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147111</v>
+        <v>129145777</v>
       </c>
       <c r="B46" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581035</v>
+        <v>580994</v>
       </c>
       <c r="R46" t="n">
-        <v>6952380</v>
+        <v>6952436</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129147338</v>
+        <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R47" t="n">
-        <v>6952297</v>
+        <v>6952419</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5255,32 +5255,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129148498</v>
+        <v>129147878</v>
       </c>
       <c r="B48" t="n">
-        <v>92192</v>
+        <v>91550</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581137</v>
+        <v>581069</v>
       </c>
       <c r="R48" t="n">
-        <v>6952306</v>
+        <v>6952305</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5352,32 +5352,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147435</v>
+        <v>129148498</v>
       </c>
       <c r="B49" t="n">
-        <v>91847</v>
+        <v>92193</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581012</v>
+        <v>581137</v>
       </c>
       <c r="R49" t="n">
-        <v>6952237</v>
+        <v>6952306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147878</v>
+        <v>129147435</v>
       </c>
       <c r="B50" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581069</v>
+        <v>581012</v>
       </c>
       <c r="R50" t="n">
-        <v>6952305</v>
+        <v>6952237</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5546,38 +5546,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147223</v>
+        <v>129145829</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5586,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581028</v>
+        <v>580986</v>
       </c>
       <c r="R51" t="n">
-        <v>6952359</v>
+        <v>6952449</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5622,11 +5621,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5653,37 +5647,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129145829</v>
+        <v>129147223</v>
       </c>
       <c r="B52" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580986</v>
+        <v>581028</v>
       </c>
       <c r="R52" t="n">
-        <v>6952449</v>
+        <v>6952359</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5728,6 +5723,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129145861</v>
+        <v>129146985</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,39 +2381,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580975</v>
+        <v>581008</v>
       </c>
       <c r="R19" t="n">
-        <v>6952488</v>
+        <v>6952388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,11 +2441,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2477,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146554</v>
+        <v>129146915</v>
       </c>
       <c r="B20" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,7 +2564,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146985</v>
+        <v>129147319</v>
       </c>
       <c r="B21" t="n">
         <v>91848</v>
@@ -2609,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581008</v>
+        <v>581032</v>
       </c>
       <c r="R21" t="n">
-        <v>6952388</v>
+        <v>6952316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2671,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146915</v>
+        <v>129146554</v>
       </c>
       <c r="B22" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2672,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129147319</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581032</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952316</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147254</v>
+        <v>129145834</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,34 +2876,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581037</v>
+        <v>580977</v>
       </c>
       <c r="R24" t="n">
-        <v>6952341</v>
+        <v>6952440</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,6 +2941,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2962,50 +2972,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129145834</v>
+        <v>129145307</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91763</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580977</v>
+        <v>581027</v>
       </c>
       <c r="R25" t="n">
-        <v>6952440</v>
+        <v>6952418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3038,11 +3043,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3069,32 +3069,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147966</v>
+        <v>129147254</v>
       </c>
       <c r="B26" t="n">
-        <v>92003</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581110</v>
+        <v>581037</v>
       </c>
       <c r="R26" t="n">
-        <v>6952279</v>
+        <v>6952341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B27" t="n">
-        <v>91763</v>
+        <v>92003</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R27" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B32" t="n">
-        <v>92003</v>
+        <v>91550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R32" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B33" t="n">
-        <v>91550</v>
+        <v>92003</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R33" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>92003</v>
+        <v>91763</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R37" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>91763</v>
+        <v>92003</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R38" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147338</v>
+        <v>129145777</v>
       </c>
       <c r="B45" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581035</v>
+        <v>580994</v>
       </c>
       <c r="R45" t="n">
-        <v>6952297</v>
+        <v>6952436</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129145777</v>
+        <v>129147338</v>
       </c>
       <c r="B46" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580994</v>
+        <v>581035</v>
       </c>
       <c r="R46" t="n">
-        <v>6952436</v>
+        <v>6952297</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5255,32 +5255,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129147878</v>
+        <v>129148498</v>
       </c>
       <c r="B48" t="n">
-        <v>91550</v>
+        <v>92193</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581069</v>
+        <v>581137</v>
       </c>
       <c r="R48" t="n">
-        <v>6952305</v>
+        <v>6952306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5352,32 +5352,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129148498</v>
+        <v>129147878</v>
       </c>
       <c r="B49" t="n">
-        <v>92193</v>
+        <v>91550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>483</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581137</v>
+        <v>581069</v>
       </c>
       <c r="R49" t="n">
-        <v>6952306</v>
+        <v>6952305</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5546,37 +5546,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129145829</v>
+        <v>129147223</v>
       </c>
       <c r="B51" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5585,10 +5586,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580986</v>
+        <v>581028</v>
       </c>
       <c r="R51" t="n">
-        <v>6952449</v>
+        <v>6952359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5621,6 +5622,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5647,38 +5653,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129147223</v>
+        <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5687,10 +5692,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581028</v>
+        <v>580986</v>
       </c>
       <c r="R52" t="n">
-        <v>6952359</v>
+        <v>6952449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5723,11 +5728,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146985</v>
+        <v>129145861</v>
       </c>
       <c r="B19" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,34 +2381,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581008</v>
+        <v>580975</v>
       </c>
       <c r="R19" t="n">
-        <v>6952388</v>
+        <v>6952488</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,6 +2446,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2467,7 +2477,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146915</v>
+        <v>129146985</v>
       </c>
       <c r="B20" t="n">
         <v>91848</v>
@@ -2502,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R20" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,7 +2574,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B21" t="n">
         <v>91848</v>
@@ -2599,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R21" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146554</v>
+        <v>129147319</v>
       </c>
       <c r="B22" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2696,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R22" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2758,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129145861</v>
+        <v>129146554</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,39 +2779,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R23" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,50 +2865,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145834</v>
+        <v>129145307</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91763</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580977</v>
+        <v>581027</v>
       </c>
       <c r="R24" t="n">
-        <v>6952440</v>
+        <v>6952418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,11 +2936,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2972,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129145307</v>
+        <v>129147254</v>
       </c>
       <c r="B25" t="n">
-        <v>91763</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3007,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581027</v>
+        <v>581037</v>
       </c>
       <c r="R25" t="n">
-        <v>6952418</v>
+        <v>6952341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,32 +3059,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147254</v>
+        <v>129147966</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>92003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3104,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581037</v>
+        <v>581110</v>
       </c>
       <c r="R26" t="n">
-        <v>6952341</v>
+        <v>6952279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3166,45 +3156,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129147966</v>
+        <v>129145834</v>
       </c>
       <c r="B27" t="n">
-        <v>92003</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581110</v>
+        <v>580977</v>
       </c>
       <c r="R27" t="n">
-        <v>6952279</v>
+        <v>6952440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,6 +3232,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3364,49 +3364,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>91848</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R29" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3465,45 +3461,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>91848</v>
+        <v>98724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R30" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91550</v>
+        <v>92003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R32" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>92003</v>
+        <v>91550</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R33" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129147948</v>
+        <v>129147998</v>
       </c>
       <c r="B41" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4577,34 +4577,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581098</v>
+        <v>581110</v>
       </c>
       <c r="R41" t="n">
-        <v>6952295</v>
+        <v>6952279</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4637,6 +4642,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4663,10 +4673,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129147998</v>
+        <v>129147948</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4674,39 +4684,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581110</v>
+        <v>581098</v>
       </c>
       <c r="R42" t="n">
-        <v>6952279</v>
+        <v>6952295</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4739,11 +4744,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013540</v>
       </c>
       <c r="B2" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129013524</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129013216</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129013417</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1382,38 +1382,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013314</v>
+        <v>129013448</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1422,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R9" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,37 +1483,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129013448</v>
+        <v>129013314</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R10" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
         <v>129145329</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>129147195</v>
       </c>
       <c r="B12" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>129145512</v>
       </c>
       <c r="B13" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>129147106</v>
       </c>
       <c r="B14" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129147978</v>
       </c>
       <c r="B15" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129147920</v>
+        <v>129146939</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>92006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581077</v>
+        <v>580964</v>
       </c>
       <c r="R17" t="n">
-        <v>6952314</v>
+        <v>6952430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129146939</v>
+        <v>129147920</v>
       </c>
       <c r="B18" t="n">
-        <v>92003</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580964</v>
+        <v>581077</v>
       </c>
       <c r="R18" t="n">
-        <v>6952430</v>
+        <v>6952314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129145861</v>
+        <v>129146985</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,39 +2381,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580975</v>
+        <v>581008</v>
       </c>
       <c r="R19" t="n">
-        <v>6952488</v>
+        <v>6952388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,11 +2441,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2477,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146985</v>
+        <v>129146915</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2512,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R20" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146915</v>
+        <v>129147319</v>
       </c>
       <c r="B21" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R21" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2671,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129147319</v>
+        <v>129146554</v>
       </c>
       <c r="B22" t="n">
-        <v>91848</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2672,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2696,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R22" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146554</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>91763</v>
+        <v>92006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R24" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147966</v>
+        <v>129145307</v>
       </c>
       <c r="B26" t="n">
-        <v>92003</v>
+        <v>91766</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,21 +3070,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581110</v>
+        <v>581027</v>
       </c>
       <c r="R26" t="n">
-        <v>6952279</v>
+        <v>6952418</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B32" t="n">
-        <v>92003</v>
+        <v>91553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R32" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B33" t="n">
-        <v>91550</v>
+        <v>92006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R33" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>91763</v>
+        <v>91766</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92241</v>
+        <v>92244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>129147948</v>
       </c>
       <c r="B42" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>129147161</v>
       </c>
       <c r="B43" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129147111</v>
       </c>
       <c r="B44" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>129145777</v>
       </c>
       <c r="B45" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>129147338</v>
       </c>
       <c r="B46" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>129148498</v>
       </c>
       <c r="B48" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147878</v>
+        <v>129147223</v>
       </c>
       <c r="B49" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,34 +5363,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581069</v>
+        <v>581028</v>
       </c>
       <c r="R49" t="n">
-        <v>6952305</v>
+        <v>6952359</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5423,6 +5428,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5449,10 +5459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147435</v>
+        <v>129147878</v>
       </c>
       <c r="B50" t="n">
-        <v>91848</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5460,21 +5470,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5484,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581012</v>
+        <v>581069</v>
       </c>
       <c r="R50" t="n">
-        <v>6952237</v>
+        <v>6952305</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5546,10 +5556,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147223</v>
+        <v>129147435</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5557,39 +5567,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581028</v>
+        <v>581012</v>
       </c>
       <c r="R51" t="n">
-        <v>6952359</v>
+        <v>6952237</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5622,11 +5627,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5656,7 +5656,7 @@
         <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1285,45 +1285,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129013342</v>
+        <v>129013448</v>
       </c>
       <c r="B8" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581088</v>
+        <v>581069</v>
       </c>
       <c r="R8" t="n">
-        <v>6952332</v>
+        <v>6952343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,49 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129013448</v>
+        <v>129013342</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581069</v>
+        <v>581088</v>
       </c>
       <c r="R9" t="n">
-        <v>6952343</v>
+        <v>6952332</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,45 +1585,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145329</v>
+        <v>129145962</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>57568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581027</v>
+        <v>580975</v>
       </c>
       <c r="R11" t="n">
-        <v>6952418</v>
+        <v>6952488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147195</v>
+        <v>129145329</v>
       </c>
       <c r="B12" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1702,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581017</v>
+        <v>581027</v>
       </c>
       <c r="R12" t="n">
-        <v>6952357</v>
+        <v>6952418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1885,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147106</v>
+        <v>129147195</v>
       </c>
       <c r="B14" t="n">
         <v>91851</v>
@@ -1911,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581035</v>
+        <v>581017</v>
       </c>
       <c r="R14" t="n">
-        <v>6952380</v>
+        <v>6952357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147978</v>
+        <v>129147106</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>91851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581098</v>
+        <v>581035</v>
       </c>
       <c r="R15" t="n">
-        <v>6952295</v>
+        <v>6952380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129145962</v>
+        <v>129147978</v>
       </c>
       <c r="B16" t="n">
-        <v>57568</v>
+        <v>91517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,43 +2090,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102621</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580975</v>
+        <v>581098</v>
       </c>
       <c r="R16" t="n">
-        <v>6952488</v>
+        <v>6952295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146985</v>
+        <v>129146554</v>
       </c>
       <c r="B19" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R19" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146915</v>
+        <v>129146985</v>
       </c>
       <c r="B20" t="n">
         <v>91851</v>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580964</v>
+        <v>581008</v>
       </c>
       <c r="R20" t="n">
-        <v>6952430</v>
+        <v>6952388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B21" t="n">
         <v>91851</v>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R21" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146554</v>
+        <v>129147319</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,21 +2672,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R22" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147966</v>
+        <v>129145307</v>
       </c>
       <c r="B24" t="n">
-        <v>92006</v>
+        <v>91766</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581110</v>
+        <v>581027</v>
       </c>
       <c r="R24" t="n">
-        <v>6952279</v>
+        <v>6952418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,45 +3059,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129145307</v>
+        <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>91766</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581027</v>
+        <v>580977</v>
       </c>
       <c r="R26" t="n">
-        <v>6952418</v>
+        <v>6952440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,6 +3135,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3156,50 +3166,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145834</v>
+        <v>129147966</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>92006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580977</v>
+        <v>581110</v>
       </c>
       <c r="R27" t="n">
-        <v>6952440</v>
+        <v>6952279</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,11 +3237,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3364,45 +3364,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B29" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R29" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,49 +3465,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R30" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129147998</v>
+        <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4577,39 +4577,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581110</v>
+        <v>581098</v>
       </c>
       <c r="R41" t="n">
-        <v>6952279</v>
+        <v>6952295</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,11 +4637,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4673,10 +4663,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129147948</v>
+        <v>129147998</v>
       </c>
       <c r="B42" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4684,34 +4674,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581098</v>
+        <v>581110</v>
       </c>
       <c r="R42" t="n">
-        <v>6952295</v>
+        <v>6952279</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4744,6 +4739,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129147161</v>
+        <v>129145366</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581019</v>
+        <v>581021</v>
       </c>
       <c r="R43" t="n">
-        <v>6952367</v>
+        <v>6952419</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129147111</v>
+        <v>129147161</v>
       </c>
       <c r="B44" t="n">
         <v>91553</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581035</v>
+        <v>581019</v>
       </c>
       <c r="R44" t="n">
-        <v>6952380</v>
+        <v>6952367</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129145777</v>
+        <v>129147111</v>
       </c>
       <c r="B45" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580994</v>
+        <v>581035</v>
       </c>
       <c r="R45" t="n">
-        <v>6952436</v>
+        <v>6952380</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129145366</v>
+        <v>129145777</v>
       </c>
       <c r="B47" t="n">
         <v>91851</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581021</v>
+        <v>580994</v>
       </c>
       <c r="R47" t="n">
-        <v>6952419</v>
+        <v>6952436</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147223</v>
+        <v>129147435</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,39 +5363,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581028</v>
+        <v>581012</v>
       </c>
       <c r="R49" t="n">
-        <v>6952359</v>
+        <v>6952237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5428,11 +5423,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5459,10 +5449,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147878</v>
+        <v>129147223</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,34 +5460,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581069</v>
+        <v>581028</v>
       </c>
       <c r="R50" t="n">
-        <v>6952305</v>
+        <v>6952359</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,6 +5525,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5556,10 +5556,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147435</v>
+        <v>129147878</v>
       </c>
       <c r="B51" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,21 +5567,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581012</v>
+        <v>581069</v>
       </c>
       <c r="R51" t="n">
-        <v>6952237</v>
+        <v>6952305</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1585,54 +1585,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145962</v>
+        <v>129145329</v>
       </c>
       <c r="B11" t="n">
-        <v>57568</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580975</v>
+        <v>581027</v>
       </c>
       <c r="R11" t="n">
-        <v>6952488</v>
+        <v>6952418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145329</v>
+        <v>129147106</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581027</v>
+        <v>581035</v>
       </c>
       <c r="R12" t="n">
-        <v>6952418</v>
+        <v>6952380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,32 +1876,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147195</v>
+        <v>129147978</v>
       </c>
       <c r="B14" t="n">
-        <v>91851</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581017</v>
+        <v>581098</v>
       </c>
       <c r="R14" t="n">
-        <v>6952357</v>
+        <v>6952295</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,7 +1973,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147106</v>
+        <v>129147195</v>
       </c>
       <c r="B15" t="n">
         <v>91851</v>
@@ -2017,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581035</v>
+        <v>581017</v>
       </c>
       <c r="R15" t="n">
-        <v>6952380</v>
+        <v>6952357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129147978</v>
+        <v>129145962</v>
       </c>
       <c r="B16" t="n">
-        <v>91517</v>
+        <v>57568</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,34 +2081,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>102621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581098</v>
+        <v>580975</v>
       </c>
       <c r="R16" t="n">
-        <v>6952295</v>
+        <v>6952488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146985</v>
+        <v>129146915</v>
       </c>
       <c r="B20" t="n">
         <v>91851</v>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R20" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146915</v>
+        <v>129145861</v>
       </c>
       <c r="B21" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,34 +2575,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R21" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2635,6 +2640,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2661,7 +2671,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129147319</v>
+        <v>129146985</v>
       </c>
       <c r="B22" t="n">
         <v>91851</v>
@@ -2696,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581032</v>
+        <v>581008</v>
       </c>
       <c r="R22" t="n">
-        <v>6952316</v>
+        <v>6952388</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2758,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129145861</v>
+        <v>129147319</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,39 +2779,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580975</v>
+        <v>581032</v>
       </c>
       <c r="R23" t="n">
-        <v>6952488</v>
+        <v>6952316</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>91766</v>
+        <v>92006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R24" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147254</v>
+        <v>129145307</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>91766</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581037</v>
+        <v>581027</v>
       </c>
       <c r="R25" t="n">
-        <v>6952341</v>
+        <v>6952418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129145834</v>
+        <v>129147254</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,39 +3070,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580977</v>
+        <v>581037</v>
       </c>
       <c r="R26" t="n">
-        <v>6952440</v>
+        <v>6952341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,11 +3130,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3166,45 +3156,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129147966</v>
+        <v>129145834</v>
       </c>
       <c r="B27" t="n">
-        <v>92006</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581110</v>
+        <v>580977</v>
       </c>
       <c r="R27" t="n">
-        <v>6952279</v>
+        <v>6952440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,6 +3232,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,32 +3669,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129145352</v>
+        <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>91553</v>
+        <v>92006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581021</v>
+        <v>581016</v>
       </c>
       <c r="R32" t="n">
-        <v>6952419</v>
+        <v>6952378</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129147019</v>
+        <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>92006</v>
+        <v>91553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581016</v>
+        <v>581021</v>
       </c>
       <c r="R33" t="n">
-        <v>6952378</v>
+        <v>6952419</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129147161</v>
+        <v>129147338</v>
       </c>
       <c r="B44" t="n">
         <v>91553</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581019</v>
+        <v>581035</v>
       </c>
       <c r="R44" t="n">
-        <v>6952367</v>
+        <v>6952297</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147111</v>
+        <v>129147161</v>
       </c>
       <c r="B45" t="n">
         <v>91553</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581035</v>
+        <v>581019</v>
       </c>
       <c r="R45" t="n">
-        <v>6952380</v>
+        <v>6952367</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147338</v>
+        <v>129147111</v>
       </c>
       <c r="B46" t="n">
         <v>91553</v>
@@ -5099,7 +5099,7 @@
         <v>581035</v>
       </c>
       <c r="R46" t="n">
-        <v>6952297</v>
+        <v>6952380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5255,32 +5255,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129148498</v>
+        <v>129147435</v>
       </c>
       <c r="B48" t="n">
-        <v>92196</v>
+        <v>91851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581137</v>
+        <v>581012</v>
       </c>
       <c r="R48" t="n">
-        <v>6952306</v>
+        <v>6952237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147435</v>
+        <v>129147878</v>
       </c>
       <c r="B49" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,21 +5363,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581012</v>
+        <v>581069</v>
       </c>
       <c r="R49" t="n">
-        <v>6952237</v>
+        <v>6952305</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,50 +5449,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147223</v>
+        <v>129148498</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>92196</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>483</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581028</v>
+        <v>581137</v>
       </c>
       <c r="R50" t="n">
-        <v>6952359</v>
+        <v>6952306</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5525,11 +5520,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5556,10 +5546,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147878</v>
+        <v>129147223</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,34 +5557,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581069</v>
+        <v>581028</v>
       </c>
       <c r="R51" t="n">
-        <v>6952305</v>
+        <v>6952359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,6 +5622,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1585,32 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129145329</v>
+        <v>129147978</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>91517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581027</v>
+        <v>581098</v>
       </c>
       <c r="R11" t="n">
-        <v>6952418</v>
+        <v>6952295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147106</v>
+        <v>129147195</v>
       </c>
       <c r="B12" t="n">
         <v>91851</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581035</v>
+        <v>581017</v>
       </c>
       <c r="R12" t="n">
-        <v>6952380</v>
+        <v>6952357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145512</v>
+        <v>129147106</v>
       </c>
       <c r="B13" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581002</v>
+        <v>581035</v>
       </c>
       <c r="R13" t="n">
-        <v>6952394</v>
+        <v>6952380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,32 +1876,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147978</v>
+        <v>129145329</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581098</v>
+        <v>581027</v>
       </c>
       <c r="R14" t="n">
-        <v>6952295</v>
+        <v>6952418</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147195</v>
+        <v>129145512</v>
       </c>
       <c r="B15" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,21 +1984,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581017</v>
+        <v>581002</v>
       </c>
       <c r="R15" t="n">
-        <v>6952357</v>
+        <v>6952394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129146554</v>
+        <v>129147319</v>
       </c>
       <c r="B19" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R19" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146915</v>
+        <v>129146554</v>
       </c>
       <c r="B20" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B23" t="n">
         <v>91851</v>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R23" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147966</v>
+        <v>129145307</v>
       </c>
       <c r="B24" t="n">
-        <v>92006</v>
+        <v>91766</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581110</v>
+        <v>581027</v>
       </c>
       <c r="R24" t="n">
-        <v>6952279</v>
+        <v>6952418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B25" t="n">
-        <v>91766</v>
+        <v>92006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R25" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147254</v>
+        <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,34 +3070,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581037</v>
+        <v>580977</v>
       </c>
       <c r="R26" t="n">
-        <v>6952341</v>
+        <v>6952440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,6 +3135,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3156,10 +3166,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145834</v>
+        <v>129147254</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,39 +3177,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580977</v>
+        <v>581037</v>
       </c>
       <c r="R27" t="n">
-        <v>6952440</v>
+        <v>6952341</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,11 +3237,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3364,49 +3364,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R29" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3465,45 +3461,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B30" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R30" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129147948</v>
+        <v>129147998</v>
       </c>
       <c r="B41" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4577,34 +4577,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581098</v>
+        <v>581110</v>
       </c>
       <c r="R41" t="n">
-        <v>6952295</v>
+        <v>6952279</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4637,6 +4642,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4663,10 +4673,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129147998</v>
+        <v>129147948</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4674,39 +4684,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581110</v>
+        <v>581098</v>
       </c>
       <c r="R42" t="n">
-        <v>6952279</v>
+        <v>6952295</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4739,11 +4744,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4770,7 +4770,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129145366</v>
+        <v>129145777</v>
       </c>
       <c r="B43" t="n">
         <v>91851</v>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581021</v>
+        <v>580994</v>
       </c>
       <c r="R43" t="n">
-        <v>6952419</v>
+        <v>6952436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129147338</v>
+        <v>129145366</v>
       </c>
       <c r="B44" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R44" t="n">
-        <v>6952297</v>
+        <v>6952419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129145777</v>
+        <v>129147338</v>
       </c>
       <c r="B47" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580994</v>
+        <v>581035</v>
       </c>
       <c r="R47" t="n">
-        <v>6952436</v>
+        <v>6952297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5449,45 +5449,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129148498</v>
+        <v>129147223</v>
       </c>
       <c r="B50" t="n">
-        <v>92196</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>483</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581137</v>
+        <v>581028</v>
       </c>
       <c r="R50" t="n">
-        <v>6952306</v>
+        <v>6952359</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5520,6 +5525,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5546,50 +5556,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147223</v>
+        <v>129148498</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>92196</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>483</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581028</v>
+        <v>581137</v>
       </c>
       <c r="R51" t="n">
-        <v>6952359</v>
+        <v>6952306</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5622,11 +5627,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1585,32 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147978</v>
+        <v>129147195</v>
       </c>
       <c r="B11" t="n">
-        <v>91517</v>
+        <v>91851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581098</v>
+        <v>581017</v>
       </c>
       <c r="R11" t="n">
-        <v>6952295</v>
+        <v>6952357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147195</v>
+        <v>129147106</v>
       </c>
       <c r="B12" t="n">
         <v>91851</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581017</v>
+        <v>581035</v>
       </c>
       <c r="R12" t="n">
-        <v>6952357</v>
+        <v>6952380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147106</v>
+        <v>129145329</v>
       </c>
       <c r="B13" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581035</v>
+        <v>581027</v>
       </c>
       <c r="R13" t="n">
-        <v>6952380</v>
+        <v>6952418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129145329</v>
+        <v>129145512</v>
       </c>
       <c r="B14" t="n">
         <v>91553</v>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581027</v>
+        <v>581002</v>
       </c>
       <c r="R14" t="n">
-        <v>6952418</v>
+        <v>6952394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,32 +1973,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129145512</v>
+        <v>129147978</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581002</v>
+        <v>581098</v>
       </c>
       <c r="R15" t="n">
-        <v>6952394</v>
+        <v>6952295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129147319</v>
+        <v>129146985</v>
       </c>
       <c r="B19" t="n">
         <v>91851</v>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581032</v>
+        <v>581008</v>
       </c>
       <c r="R19" t="n">
-        <v>6952316</v>
+        <v>6952388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146554</v>
+        <v>129147319</v>
       </c>
       <c r="B20" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R20" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129145861</v>
+        <v>129146915</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,39 +2575,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R21" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2640,11 +2635,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2671,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146985</v>
+        <v>129146554</v>
       </c>
       <c r="B22" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2672,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2696,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581008</v>
+        <v>580964</v>
       </c>
       <c r="R22" t="n">
-        <v>6952388</v>
+        <v>6952430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146915</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129145834</v>
+        <v>129147254</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,39 +3070,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580977</v>
+        <v>581037</v>
       </c>
       <c r="R26" t="n">
-        <v>6952440</v>
+        <v>6952341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,11 +3130,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3166,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129147254</v>
+        <v>129145834</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3177,34 +3167,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581037</v>
+        <v>580977</v>
       </c>
       <c r="R27" t="n">
-        <v>6952341</v>
+        <v>6952440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,6 +3232,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3364,45 +3364,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129146557</v>
+        <v>129146457</v>
       </c>
       <c r="B29" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580965</v>
+        <v>580954</v>
       </c>
       <c r="R29" t="n">
-        <v>6952443</v>
+        <v>6952482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,49 +3465,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129146457</v>
+        <v>129146557</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580954</v>
+        <v>580965</v>
       </c>
       <c r="R30" t="n">
-        <v>6952482</v>
+        <v>6952443</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129147998</v>
+        <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4577,39 +4577,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581110</v>
+        <v>581098</v>
       </c>
       <c r="R41" t="n">
-        <v>6952279</v>
+        <v>6952295</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,11 +4637,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4673,10 +4663,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129147948</v>
+        <v>129147998</v>
       </c>
       <c r="B42" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4684,34 +4674,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581098</v>
+        <v>581110</v>
       </c>
       <c r="R42" t="n">
-        <v>6952295</v>
+        <v>6952279</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4744,6 +4739,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129145777</v>
+        <v>129147161</v>
       </c>
       <c r="B43" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580994</v>
+        <v>581019</v>
       </c>
       <c r="R43" t="n">
-        <v>6952436</v>
+        <v>6952367</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145366</v>
+        <v>129147111</v>
       </c>
       <c r="B44" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R44" t="n">
-        <v>6952419</v>
+        <v>6952380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147161</v>
+        <v>129147338</v>
       </c>
       <c r="B45" t="n">
         <v>91553</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581019</v>
+        <v>581035</v>
       </c>
       <c r="R45" t="n">
-        <v>6952367</v>
+        <v>6952297</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147111</v>
+        <v>129145777</v>
       </c>
       <c r="B46" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581035</v>
+        <v>580994</v>
       </c>
       <c r="R46" t="n">
-        <v>6952380</v>
+        <v>6952436</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129147338</v>
+        <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R47" t="n">
-        <v>6952297</v>
+        <v>6952419</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5352,32 +5352,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147878</v>
+        <v>129148498</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>92196</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>483</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581069</v>
+        <v>581137</v>
       </c>
       <c r="R49" t="n">
-        <v>6952305</v>
+        <v>6952306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147223</v>
+        <v>129147878</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5460,39 +5460,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581028</v>
+        <v>581069</v>
       </c>
       <c r="R50" t="n">
-        <v>6952359</v>
+        <v>6952305</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5525,11 +5520,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5556,45 +5546,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129148498</v>
+        <v>129147223</v>
       </c>
       <c r="B51" t="n">
-        <v>92196</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>483</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581137</v>
+        <v>581028</v>
       </c>
       <c r="R51" t="n">
-        <v>6952306</v>
+        <v>6952359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,6 +5622,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1973,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147978</v>
+        <v>129145962</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>57568</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,34 +1984,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>102621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581098</v>
+        <v>580975</v>
       </c>
       <c r="R15" t="n">
-        <v>6952295</v>
+        <v>6952488</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129145962</v>
+        <v>129147978</v>
       </c>
       <c r="B16" t="n">
-        <v>57568</v>
+        <v>91517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,43 +2090,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102621</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580975</v>
+        <v>581098</v>
       </c>
       <c r="R16" t="n">
-        <v>6952488</v>
+        <v>6952295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129147319</v>
+        <v>129146915</v>
       </c>
       <c r="B20" t="n">
         <v>91851</v>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581032</v>
+        <v>580964</v>
       </c>
       <c r="R20" t="n">
-        <v>6952316</v>
+        <v>6952430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146915</v>
+        <v>129147319</v>
       </c>
       <c r="B21" t="n">
         <v>91851</v>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580964</v>
+        <v>581032</v>
       </c>
       <c r="R21" t="n">
-        <v>6952430</v>
+        <v>6952316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146554</v>
+        <v>129145861</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,34 +2672,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R22" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,6 +2737,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2758,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129145861</v>
+        <v>129146554</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,39 +2779,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R23" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129145307</v>
+        <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>91766</v>
+        <v>92006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581027</v>
+        <v>581110</v>
       </c>
       <c r="R24" t="n">
-        <v>6952418</v>
+        <v>6952279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129147966</v>
+        <v>129147254</v>
       </c>
       <c r="B25" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581110</v>
+        <v>581037</v>
       </c>
       <c r="R25" t="n">
-        <v>6952279</v>
+        <v>6952341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,32 +3059,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129147254</v>
+        <v>129145307</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>91766</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581037</v>
+        <v>581027</v>
       </c>
       <c r="R26" t="n">
-        <v>6952341</v>
+        <v>6952418</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129147161</v>
+        <v>129145777</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581019</v>
+        <v>580994</v>
       </c>
       <c r="R43" t="n">
-        <v>6952367</v>
+        <v>6952436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129147111</v>
+        <v>129145366</v>
       </c>
       <c r="B44" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R44" t="n">
-        <v>6952380</v>
+        <v>6952419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147338</v>
+        <v>129147161</v>
       </c>
       <c r="B45" t="n">
         <v>91553</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581035</v>
+        <v>581019</v>
       </c>
       <c r="R45" t="n">
-        <v>6952297</v>
+        <v>6952367</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129145777</v>
+        <v>129147111</v>
       </c>
       <c r="B46" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580994</v>
+        <v>581035</v>
       </c>
       <c r="R46" t="n">
-        <v>6952436</v>
+        <v>6952380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129145366</v>
+        <v>129147338</v>
       </c>
       <c r="B47" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581021</v>
+        <v>581035</v>
       </c>
       <c r="R47" t="n">
-        <v>6952419</v>
+        <v>6952297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5255,32 +5255,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129147435</v>
+        <v>129148498</v>
       </c>
       <c r="B48" t="n">
-        <v>91851</v>
+        <v>92196</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581012</v>
+        <v>581137</v>
       </c>
       <c r="R48" t="n">
-        <v>6952237</v>
+        <v>6952306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5352,32 +5352,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129148498</v>
+        <v>129147435</v>
       </c>
       <c r="B49" t="n">
-        <v>92196</v>
+        <v>91851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>483</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581137</v>
+        <v>581012</v>
       </c>
       <c r="R49" t="n">
-        <v>6952306</v>
+        <v>6952237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5546,38 +5546,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129147223</v>
+        <v>129145829</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5586,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581028</v>
+        <v>580986</v>
       </c>
       <c r="R51" t="n">
-        <v>6952359</v>
+        <v>6952449</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5622,11 +5621,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5653,37 +5647,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129145829</v>
+        <v>129147223</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580986</v>
+        <v>581028</v>
       </c>
       <c r="R52" t="n">
-        <v>6952449</v>
+        <v>6952359</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5728,6 +5723,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147195</v>
+        <v>129145329</v>
       </c>
       <c r="B11" t="n">
-        <v>91851</v>
+        <v>91581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581017</v>
+        <v>581027</v>
       </c>
       <c r="R11" t="n">
-        <v>6952357</v>
+        <v>6952418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147106</v>
+        <v>129147195</v>
       </c>
       <c r="B12" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581035</v>
+        <v>581017</v>
       </c>
       <c r="R12" t="n">
-        <v>6952380</v>
+        <v>6952357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145329</v>
+        <v>129147106</v>
       </c>
       <c r="B13" t="n">
-        <v>91553</v>
+        <v>91879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581027</v>
+        <v>581035</v>
       </c>
       <c r="R13" t="n">
-        <v>6952418</v>
+        <v>6952380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>129145512</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129145962</v>
+        <v>129147978</v>
       </c>
       <c r="B15" t="n">
-        <v>57568</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,43 +1984,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102621</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580975</v>
+        <v>581098</v>
       </c>
       <c r="R15" t="n">
-        <v>6952488</v>
+        <v>6952295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129147978</v>
+        <v>129145962</v>
       </c>
       <c r="B16" t="n">
-        <v>91517</v>
+        <v>57571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,34 +2081,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>102621</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581098</v>
+        <v>580975</v>
       </c>
       <c r="R16" t="n">
-        <v>6952295</v>
+        <v>6952488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,7 +2179,7 @@
         <v>129146939</v>
       </c>
       <c r="B17" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>129147920</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>129146985</v>
       </c>
       <c r="B19" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129146915</v>
+        <v>129146554</v>
       </c>
       <c r="B20" t="n">
-        <v>91851</v>
+        <v>91581</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
         <v>129147319</v>
       </c>
       <c r="B21" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129145861</v>
+        <v>129146915</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,39 +2672,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580975</v>
+        <v>580964</v>
       </c>
       <c r="R22" t="n">
-        <v>6952488</v>
+        <v>6952430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,11 +2732,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2768,10 +2758,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146554</v>
+        <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>57730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,34 +2769,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580964</v>
+        <v>580975</v>
       </c>
       <c r="R23" t="n">
-        <v>6952430</v>
+        <v>6952488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2834,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2868,7 +2868,7 @@
         <v>129147966</v>
       </c>
       <c r="B24" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129147254</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3059,45 +3059,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129145307</v>
+        <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>91766</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581027</v>
+        <v>580977</v>
       </c>
       <c r="R26" t="n">
-        <v>6952418</v>
+        <v>6952440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,6 +3135,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3156,50 +3166,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129145834</v>
+        <v>129145307</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>91794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580977</v>
+        <v>581027</v>
       </c>
       <c r="R27" t="n">
-        <v>6952440</v>
+        <v>6952418</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,11 +3237,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3266,7 +3266,7 @@
         <v>129147908</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>129146457</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>129146557</v>
       </c>
       <c r="B30" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129147381</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>129147019</v>
       </c>
       <c r="B32" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>129145352</v>
       </c>
       <c r="B33" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>129147282</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>129145294</v>
       </c>
       <c r="B35" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129147892</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129148349</v>
       </c>
       <c r="B37" t="n">
-        <v>91766</v>
+        <v>91794</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129145405</v>
       </c>
       <c r="B38" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>129147052</v>
       </c>
       <c r="B39" t="n">
-        <v>92244</v>
+        <v>92272</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129146510</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129147948</v>
       </c>
       <c r="B41" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>129147998</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129145777</v>
+        <v>129147338</v>
       </c>
       <c r="B43" t="n">
-        <v>91851</v>
+        <v>91581</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580994</v>
+        <v>581035</v>
       </c>
       <c r="R43" t="n">
-        <v>6952436</v>
+        <v>6952297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145366</v>
+        <v>129147161</v>
       </c>
       <c r="B44" t="n">
-        <v>91851</v>
+        <v>91581</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581021</v>
+        <v>581019</v>
       </c>
       <c r="R44" t="n">
-        <v>6952419</v>
+        <v>6952367</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129147161</v>
+        <v>129147111</v>
       </c>
       <c r="B45" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581019</v>
+        <v>581035</v>
       </c>
       <c r="R45" t="n">
-        <v>6952367</v>
+        <v>6952380</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129147111</v>
+        <v>129145777</v>
       </c>
       <c r="B46" t="n">
-        <v>91553</v>
+        <v>91879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581035</v>
+        <v>580994</v>
       </c>
       <c r="R46" t="n">
-        <v>6952380</v>
+        <v>6952436</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129147338</v>
+        <v>129145366</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>91879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581035</v>
+        <v>581021</v>
       </c>
       <c r="R47" t="n">
-        <v>6952297</v>
+        <v>6952419</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5255,45 +5255,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129148498</v>
+        <v>129147223</v>
       </c>
       <c r="B48" t="n">
-        <v>92196</v>
+        <v>57730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581137</v>
+        <v>581028</v>
       </c>
       <c r="R48" t="n">
-        <v>6952306</v>
+        <v>6952359</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5326,6 +5331,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5352,32 +5362,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129147435</v>
+        <v>129148498</v>
       </c>
       <c r="B49" t="n">
-        <v>91851</v>
+        <v>92224</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>483</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5387,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581012</v>
+        <v>581137</v>
       </c>
       <c r="R49" t="n">
-        <v>6952237</v>
+        <v>6952306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,10 +5459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129147878</v>
+        <v>129147435</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>91879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5460,21 +5470,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5484,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581069</v>
+        <v>581012</v>
       </c>
       <c r="R50" t="n">
-        <v>6952305</v>
+        <v>6952237</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5546,49 +5556,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129145829</v>
+        <v>129147878</v>
       </c>
       <c r="B51" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Drolsviken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580986</v>
+        <v>581069</v>
       </c>
       <c r="R51" t="n">
-        <v>6952449</v>
+        <v>6952305</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,38 +5653,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129147223</v>
+        <v>129145829</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5687,10 +5692,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581028</v>
+        <v>580986</v>
       </c>
       <c r="R52" t="n">
-        <v>6952359</v>
+        <v>6952449</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5723,11 +5728,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -4174,10 +4174,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148349</v>
+        <v>129145405</v>
       </c>
       <c r="B37" t="n">
-        <v>91794</v>
+        <v>92034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,21 +4185,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581129</v>
+        <v>581012</v>
       </c>
       <c r="R37" t="n">
-        <v>6952292</v>
+        <v>6952414</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129145405</v>
+        <v>129148349</v>
       </c>
       <c r="B38" t="n">
-        <v>92034</v>
+        <v>91794</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581012</v>
+        <v>581129</v>
       </c>
       <c r="R38" t="n">
-        <v>6952414</v>
+        <v>6952292</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>129013513</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129013351</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>57730</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129147381</v>
       </c>
       <c r="B31" t="n">
-        <v>57730</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>129147282</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129147892</v>
       </c>
       <c r="B36" t="n">
-        <v>57730</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>129147998</v>
       </c>
       <c r="B42" t="n">
-        <v>57730</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>129147223</v>
       </c>
       <c r="B48" t="n">
-        <v>57730</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 46599-2025 artfynd.xlsx
+++ b/artfynd/A 46599-2025 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>129013513</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129013351</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>129145861</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129145834</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>129147381</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>129147282</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129147892</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>129147998</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>129147223</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
